--- a/evidence/model_runs/full_run/forecasting_intelligence_results.xlsx
+++ b/evidence/model_runs/full_run/forecasting_intelligence_results.xlsx
@@ -4221,10 +4221,10 @@
         <v>962.1692021393277</v>
       </c>
       <c r="D2" t="n">
-        <v>879.4835620288205</v>
+        <v>873.8848973812406</v>
       </c>
       <c r="E2" t="n">
-        <v>1050.002708330912</v>
+        <v>1040.022401863612</v>
       </c>
     </row>
     <row r="3">
@@ -4238,10 +4238,10 @@
         <v>1030.778325039708</v>
       </c>
       <c r="D3" t="n">
-        <v>948.6987469069375</v>
+        <v>951.4804705685251</v>
       </c>
       <c r="E3" t="n">
-        <v>1115.37488536348</v>
+        <v>1110.196416232553</v>
       </c>
     </row>
     <row r="4">
@@ -4255,10 +4255,10 @@
         <v>1283.746853165454</v>
       </c>
       <c r="D4" t="n">
-        <v>1204.045387099947</v>
+        <v>1202.641005095333</v>
       </c>
       <c r="E4" t="n">
-        <v>1370.488604191582</v>
+        <v>1358.814408742294</v>
       </c>
     </row>
     <row r="5">
@@ -4272,10 +4272,10 @@
         <v>1128.191558875007</v>
       </c>
       <c r="D5" t="n">
-        <v>1045.015935463295</v>
+        <v>1043.114671004178</v>
       </c>
       <c r="E5" t="n">
-        <v>1209.475066212878</v>
+        <v>1208.39463468718</v>
       </c>
     </row>
     <row r="6">
@@ -4289,10 +4289,10 @@
         <v>1068.455634558751</v>
       </c>
       <c r="D6" t="n">
-        <v>982.7138925774534</v>
+        <v>989.7928569117295</v>
       </c>
       <c r="E6" t="n">
-        <v>1147.856305936093</v>
+        <v>1148.968681343495</v>
       </c>
     </row>
     <row r="7">
@@ -4306,10 +4306,10 @@
         <v>1179.29771361325</v>
       </c>
       <c r="D7" t="n">
-        <v>1095.530309619512</v>
+        <v>1095.486026178335</v>
       </c>
       <c r="E7" t="n">
-        <v>1265.875446779607</v>
+        <v>1258.285690911919</v>
       </c>
     </row>
     <row r="8">
@@ -4323,10 +4323,10 @@
         <v>947.3831145332064</v>
       </c>
       <c r="D8" t="n">
-        <v>869.7751074254232</v>
+        <v>866.0073077557971</v>
       </c>
       <c r="E8" t="n">
-        <v>1033.356312822902</v>
+        <v>1025.892184863397</v>
       </c>
     </row>
     <row r="9">
@@ -4340,10 +4340,10 @@
         <v>1143.146663562603</v>
       </c>
       <c r="D9" t="n">
-        <v>1057.713937304233</v>
+        <v>1059.439589361591</v>
       </c>
       <c r="E9" t="n">
-        <v>1222.024503759708</v>
+        <v>1222.311450439312</v>
       </c>
     </row>
     <row r="10">
@@ -4357,10 +4357,10 @@
         <v>1025.867455006929</v>
       </c>
       <c r="D10" t="n">
-        <v>945.3755197658819</v>
+        <v>946.4245357641939</v>
       </c>
       <c r="E10" t="n">
-        <v>1104.091318239164</v>
+        <v>1105.999417428207</v>
       </c>
     </row>
     <row r="11">
@@ -4374,10 +4374,10 @@
         <v>1092.889005742891</v>
       </c>
       <c r="D11" t="n">
-        <v>1015.81539761131</v>
+        <v>1017.02913714046</v>
       </c>
       <c r="E11" t="n">
-        <v>1175.570078889343</v>
+        <v>1172.704201360264</v>
       </c>
     </row>
     <row r="12">
@@ -4391,10 +4391,10 @@
         <v>1123.456626645416</v>
       </c>
       <c r="D12" t="n">
-        <v>1034.614884287572</v>
+        <v>1046.034682038108</v>
       </c>
       <c r="E12" t="n">
-        <v>1205.940929374182</v>
+        <v>1204.091125966684</v>
       </c>
     </row>
     <row r="13">
@@ -4408,10 +4408,10 @@
         <v>1249.843617522131</v>
       </c>
       <c r="D13" t="n">
-        <v>1166.5800367697</v>
+        <v>1167.895260925786</v>
       </c>
       <c r="E13" t="n">
-        <v>1332.969777426803</v>
+        <v>1338.039071295973</v>
       </c>
     </row>
     <row r="14">
@@ -4425,10 +4425,10 @@
         <v>988.8503877307903</v>
       </c>
       <c r="D14" t="n">
-        <v>903.7518180999449</v>
+        <v>900.6807699122037</v>
       </c>
       <c r="E14" t="n">
-        <v>1070.106286978481</v>
+        <v>1079.275094539131</v>
       </c>
     </row>
     <row r="15">
@@ -4442,10 +4442,10 @@
         <v>943.0587038438273</v>
       </c>
       <c r="D15" t="n">
-        <v>860.9165151879744</v>
+        <v>860.1077469184006</v>
       </c>
       <c r="E15" t="n">
-        <v>1024.009076593676</v>
+        <v>1028.925711445974</v>
       </c>
     </row>
     <row r="16">
@@ -4459,10 +4459,10 @@
         <v>1138.998190676004</v>
       </c>
       <c r="D16" t="n">
-        <v>1060.630143379141</v>
+        <v>1062.248258338186</v>
       </c>
       <c r="E16" t="n">
-        <v>1225.239623470836</v>
+        <v>1217.247289075816</v>
       </c>
     </row>
     <row r="17">
@@ -4476,10 +4476,10 @@
         <v>1021.894919923505</v>
       </c>
       <c r="D17" t="n">
-        <v>943.0240405369997</v>
+        <v>945.8033400800518</v>
       </c>
       <c r="E17" t="n">
-        <v>1108.159026289068</v>
+        <v>1107.654889450424</v>
       </c>
     </row>
     <row r="18">
@@ -4493,10 +4493,10 @@
         <v>1089.092408462396</v>
       </c>
       <c r="D18" t="n">
-        <v>1009.570870984512</v>
+        <v>1005.382525688793</v>
       </c>
       <c r="E18" t="n">
-        <v>1175.627496056784</v>
+        <v>1168.015248929887</v>
       </c>
     </row>
     <row r="19">
@@ -4510,10 +4510,10 @@
         <v>1119.894613102127</v>
       </c>
       <c r="D19" t="n">
-        <v>1038.588612438021</v>
+        <v>1031.715566716566</v>
       </c>
       <c r="E19" t="n">
-        <v>1207.913214360684</v>
+        <v>1202.652084360527</v>
       </c>
     </row>
     <row r="20">
@@ -4527,10 +4527,10 @@
         <v>1060.451918457339</v>
       </c>
       <c r="D20" t="n">
-        <v>977.1780412053215</v>
+        <v>983.3174285450214</v>
       </c>
       <c r="E20" t="n">
-        <v>1137.636245076777</v>
+        <v>1143.615959005027</v>
       </c>
     </row>
     <row r="21">
@@ -4544,10 +4544,10 @@
         <v>985.6988957279311</v>
       </c>
       <c r="D21" t="n">
-        <v>905.9628341802443</v>
+        <v>900.5905617787151</v>
       </c>
       <c r="E21" t="n">
-        <v>1067.298177384474</v>
+        <v>1071.160402235736</v>
       </c>
     </row>
     <row r="22">
@@ -4561,10 +4561,10 @@
         <v>1126.206064836715</v>
       </c>
       <c r="D22" t="n">
-        <v>1037.687545104273</v>
+        <v>1040.979731619311</v>
       </c>
       <c r="E22" t="n">
-        <v>1212.994750608592</v>
+        <v>1205.983484587696</v>
       </c>
     </row>
     <row r="23">
@@ -4578,10 +4578,10 @@
         <v>950.4275346917199</v>
       </c>
       <c r="D23" t="n">
-        <v>871.5208168469703</v>
+        <v>869.3011500259454</v>
       </c>
       <c r="E23" t="n">
-        <v>1032.331844652012</v>
+        <v>1033.427730584134</v>
       </c>
     </row>
     <row r="24">
@@ -4595,10 +4595,10 @@
         <v>1019.564471000875</v>
       </c>
       <c r="D24" t="n">
-        <v>936.7180716300045</v>
+        <v>933.8365729862066</v>
       </c>
       <c r="E24" t="n">
-        <v>1105.565707436919</v>
+        <v>1099.513111899707</v>
       </c>
     </row>
     <row r="25">
@@ -4612,10 +4612,10 @@
         <v>1273.060812535736</v>
       </c>
       <c r="D25" t="n">
-        <v>1184.759356848083</v>
+        <v>1188.934291554838</v>
       </c>
       <c r="E25" t="n">
-        <v>1354.426056148558</v>
+        <v>1361.389959148165</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         <v>1118.150623522643</v>
       </c>
       <c r="D26" t="n">
-        <v>1031.838951134715</v>
+        <v>1033.577848581839</v>
       </c>
       <c r="E26" t="n">
-        <v>1202.071591367843</v>
+        <v>1207.813284911017</v>
       </c>
     </row>
     <row r="27">
@@ -4646,10 +4646,10 @@
         <v>1059.001158549331</v>
       </c>
       <c r="D27" t="n">
-        <v>973.8922422687133</v>
+        <v>975.2745697849274</v>
       </c>
       <c r="E27" t="n">
-        <v>1141.193584446745</v>
+        <v>1149.997859570091</v>
       </c>
     </row>
     <row r="28">
@@ -4663,10 +4663,10 @@
         <v>984.6000114258054</v>
       </c>
       <c r="D28" t="n">
-        <v>899.0121379899366</v>
+        <v>900.5853943991922</v>
       </c>
       <c r="E28" t="n">
-        <v>1076.146845707968</v>
+        <v>1072.002596451141</v>
       </c>
     </row>
     <row r="29">
@@ -4680,10 +4680,10 @@
         <v>939.3947868817838</v>
       </c>
       <c r="D29" t="n">
-        <v>860.1114097264482</v>
+        <v>856.1426756682807</v>
       </c>
       <c r="E29" t="n">
-        <v>1021.979070117941</v>
+        <v>1023.660121468369</v>
       </c>
     </row>
     <row r="30">
@@ -4697,10 +4697,10 @@
         <v>949.9151097328224</v>
       </c>
       <c r="D30" t="n">
-        <v>863.7463332838132</v>
+        <v>865.2402031728727</v>
       </c>
       <c r="E30" t="n">
-        <v>1030.757717726316</v>
+        <v>1033.901507981395</v>
       </c>
     </row>
     <row r="31">
@@ -4714,10 +4714,10 @@
         <v>1019.345275713588</v>
       </c>
       <c r="D31" t="n">
-        <v>934.5832606336542</v>
+        <v>934.0140467895823</v>
       </c>
       <c r="E31" t="n">
-        <v>1103.361864795755</v>
+        <v>1104.428819157989</v>
       </c>
     </row>
     <row r="32">
@@ -4731,10 +4731,10 @@
         <v>1087.187869529677</v>
       </c>
       <c r="D32" t="n">
-        <v>1006.839660892966</v>
+        <v>997.1126160660903</v>
       </c>
       <c r="E32" t="n">
-        <v>1177.035482976598</v>
+        <v>1175.132523746455</v>
       </c>
     </row>
     <row r="33">
@@ -4748,10 +4748,10 @@
         <v>1118.57653351274</v>
       </c>
       <c r="D33" t="n">
-        <v>1038.976880004279</v>
+        <v>1036.808343518768</v>
       </c>
       <c r="E33" t="n">
-        <v>1204.935975997397</v>
+        <v>1205.152387822533</v>
       </c>
     </row>
     <row r="34">
@@ -4765,10 +4765,10 @@
         <v>1059.837590079571</v>
       </c>
       <c r="D34" t="n">
-        <v>970.0180716566454</v>
+        <v>970.3073289431801</v>
       </c>
       <c r="E34" t="n">
-        <v>1146.229925578843</v>
+        <v>1147.469119078193</v>
       </c>
     </row>
     <row r="35">
@@ -4782,10 +4782,10 @@
         <v>985.7296726276643</v>
       </c>
       <c r="D35" t="n">
-        <v>900.9760084267757</v>
+        <v>895.1688752447011</v>
       </c>
       <c r="E35" t="n">
-        <v>1067.978457138612</v>
+        <v>1068.048334149026</v>
       </c>
     </row>
     <row r="36">
@@ -4799,10 +4799,10 @@
         <v>940.8763236895538</v>
       </c>
       <c r="D36" t="n">
-        <v>852.4305880810925</v>
+        <v>853.4076481107667</v>
       </c>
       <c r="E36" t="n">
-        <v>1021.672405783526</v>
+        <v>1023.626175355532</v>
       </c>
     </row>
     <row r="37">
@@ -4816,10 +4816,10 @@
         <v>951.689876212027</v>
       </c>
       <c r="D37" t="n">
-        <v>870.3997791127464</v>
+        <v>863.6581228614967</v>
       </c>
       <c r="E37" t="n">
-        <v>1032.868619657354</v>
+        <v>1036.808684024212</v>
       </c>
     </row>
     <row r="38">
@@ -4833,10 +4833,10 @@
         <v>1021.530563733201</v>
       </c>
       <c r="D38" t="n">
-        <v>936.2017676106852</v>
+        <v>932.0929403387638</v>
       </c>
       <c r="E38" t="n">
-        <v>1107.761818512279</v>
+        <v>1104.64411316404</v>
       </c>
     </row>
     <row r="39">
@@ -4850,10 +4850,10 @@
         <v>1089.666387220844</v>
       </c>
       <c r="D39" t="n">
-        <v>1007.015174168586</v>
+        <v>1005.330437185114</v>
       </c>
       <c r="E39" t="n">
-        <v>1182.645510632381</v>
+        <v>1182.18587402896</v>
       </c>
     </row>
     <row r="40">
@@ -4867,10 +4867,10 @@
         <v>1307.412550134147</v>
       </c>
       <c r="D40" t="n">
-        <v>1220.962369950959</v>
+        <v>1216.227288667243</v>
       </c>
       <c r="E40" t="n">
-        <v>1396.978382934799</v>
+        <v>1402.482210346042</v>
       </c>
     </row>
     <row r="41">
@@ -4884,10 +4884,10 @@
         <v>1062.961213048104</v>
       </c>
       <c r="D41" t="n">
-        <v>968.5871529987303</v>
+        <v>971.3979004662799</v>
       </c>
       <c r="E41" t="n">
-        <v>1151.104376432733</v>
+        <v>1151.974249835048</v>
       </c>
     </row>
     <row r="42">
@@ -4901,10 +4901,10 @@
         <v>989.1465252677654</v>
       </c>
       <c r="D42" t="n">
-        <v>898.3036435156696</v>
+        <v>897.294232835902</v>
       </c>
       <c r="E42" t="n">
-        <v>1077.768236676466</v>
+        <v>1077.658871327215</v>
       </c>
     </row>
     <row r="43">
@@ -4918,10 +4918,10 @@
         <v>944.5864060013764</v>
       </c>
       <c r="D43" t="n">
-        <v>851.8237244721876</v>
+        <v>848.7572318928025</v>
       </c>
       <c r="E43" t="n">
-        <v>1039.082125167921</v>
+        <v>1032.126998533526</v>
       </c>
     </row>
     <row r="44">
@@ -4935,10 +4935,10 @@
         <v>1141.757457454071</v>
       </c>
       <c r="D44" t="n">
-        <v>1054.244367427963</v>
+        <v>1044.778212202573</v>
       </c>
       <c r="E44" t="n">
-        <v>1234.516181499083</v>
+        <v>1235.058161681878</v>
       </c>
     </row>
     <row r="45">
@@ -4952,10 +4952,10 @@
         <v>1025.885751322439</v>
       </c>
       <c r="D45" t="n">
-        <v>933.809334194577</v>
+        <v>938.9219186288365</v>
       </c>
       <c r="E45" t="n">
-        <v>1115.347318215714</v>
+        <v>1114.46930924624</v>
       </c>
     </row>
     <row r="46">
@@ -4969,10 +4969,10 @@
         <v>1094.314804481656</v>
       </c>
       <c r="D46" t="n">
-        <v>1003.372125428594</v>
+        <v>1003.676008311036</v>
       </c>
       <c r="E46" t="n">
-        <v>1188.837050954622</v>
+        <v>1186.503885109384</v>
       </c>
     </row>
     <row r="47">
@@ -4986,10 +4986,10 @@
         <v>1312.354197066471</v>
       </c>
       <c r="D47" t="n">
-        <v>1221.803798319066</v>
+        <v>1221.579581455157</v>
       </c>
       <c r="E47" t="n">
-        <v>1412.578216720298</v>
+        <v>1399.471850728366</v>
       </c>
     </row>
     <row r="48">
@@ -5003,10 +5003,10 @@
         <v>1068.137443717963</v>
       </c>
       <c r="D48" t="n">
-        <v>976.2073070424832</v>
+        <v>974.8919662061238</v>
       </c>
       <c r="E48" t="n">
-        <v>1168.184522157902</v>
+        <v>1164.558630183823</v>
       </c>
     </row>
     <row r="49">
@@ -5020,10 +5020,10 @@
         <v>1180.621608933279</v>
       </c>
       <c r="D49" t="n">
-        <v>1080.83259454584</v>
+        <v>1082.566913765992</v>
       </c>
       <c r="E49" t="n">
-        <v>1281.319901796931</v>
+        <v>1276.599199349947</v>
       </c>
     </row>
     <row r="50">
@@ -5037,10 +5037,10 @@
         <v>950.349096014085</v>
       </c>
       <c r="D50" t="n">
-        <v>858.4068485343454</v>
+        <v>859.2136467265335</v>
       </c>
       <c r="E50" t="n">
-        <v>1052.04523967331</v>
+        <v>1046.834187721611</v>
       </c>
     </row>
     <row r="51">
@@ -5054,10 +5054,10 @@
         <v>961.749107879724</v>
       </c>
       <c r="D51" t="n">
-        <v>867.1898702918912</v>
+        <v>862.8585794281937</v>
       </c>
       <c r="E51" t="n">
-        <v>1059.417544328537</v>
+        <v>1057.770605632805</v>
       </c>
     </row>
     <row r="52">
@@ -5071,10 +5071,10 @@
         <v>1032.058962875448</v>
       </c>
       <c r="D52" t="n">
-        <v>925.8641907141053</v>
+        <v>937.0451986286814</v>
       </c>
       <c r="E52" t="n">
-        <v>1136.47957818366</v>
+        <v>1131.026190387956</v>
       </c>
     </row>
     <row r="53">
@@ -5088,10 +5088,10 @@
         <v>1100.722599771904</v>
       </c>
       <c r="D53" t="n">
-        <v>998.9105390029807</v>
+        <v>1003.554306196768</v>
       </c>
       <c r="E53" t="n">
-        <v>1196.71602006146</v>
+        <v>1202.581649893743</v>
       </c>
     </row>
     <row r="54">
@@ -5105,10 +5105,10 @@
         <v>1132.932306835204</v>
       </c>
       <c r="D54" t="n">
-        <v>1036.33276790419</v>
+        <v>1030.466984948623</v>
       </c>
       <c r="E54" t="n">
-        <v>1235.559067780697</v>
+        <v>1228.745011349474</v>
       </c>
     </row>
     <row r="55">
@@ -5122,10 +5122,10 @@
         <v>1074.897114614004</v>
       </c>
       <c r="D55" t="n">
-        <v>984.710545584732</v>
+        <v>978.8249230783932</v>
       </c>
       <c r="E55" t="n">
-        <v>1177.794898145446</v>
+        <v>1178.736223586651</v>
       </c>
     </row>
     <row r="56">
@@ -5139,10 +5139,10 @@
         <v>1187.557217632286</v>
       </c>
       <c r="D56" t="n">
-        <v>1087.525819223935</v>
+        <v>1078.861216593309</v>
       </c>
       <c r="E56" t="n">
-        <v>1293.420088211557</v>
+        <v>1283.641434149613</v>
       </c>
     </row>
     <row r="57">
@@ -5156,10 +5156,10 @@
         <v>957.4019965817456</v>
       </c>
       <c r="D57" t="n">
-        <v>854.929142929545</v>
+        <v>857.0980726885821</v>
       </c>
       <c r="E57" t="n">
-        <v>1050.774368141035</v>
+        <v>1057.464844030108</v>
       </c>
     </row>
     <row r="58">
@@ -5173,10 +5173,10 @@
         <v>968.9779462503585</v>
       </c>
       <c r="D58" t="n">
-        <v>871.7111993335209</v>
+        <v>859.3496070353344</v>
       </c>
       <c r="E58" t="n">
-        <v>1076.980803187628</v>
+        <v>1077.643743550102</v>
       </c>
     </row>
     <row r="59">
@@ -5190,10 +5190,10 @@
         <v>1039.405093114427</v>
       </c>
       <c r="D59" t="n">
-        <v>927.4558238867709</v>
+        <v>934.6070536466115</v>
       </c>
       <c r="E59" t="n">
-        <v>1139.195069992774</v>
+        <v>1145.671830633755</v>
       </c>
     </row>
     <row r="60">
@@ -5207,10 +5207,10 @@
         <v>1108.186021879571</v>
       </c>
       <c r="D60" t="n">
-        <v>1002.163490074467</v>
+        <v>1005.41046386211</v>
       </c>
       <c r="E60" t="n">
-        <v>1211.587339667504</v>
+        <v>1216.268971975923</v>
       </c>
     </row>
     <row r="61">
@@ -5224,10 +5224,10 @@
         <v>1140.454374877382</v>
       </c>
       <c r="D61" t="n">
-        <v>1040.031636589909</v>
+        <v>1034.504643151468</v>
       </c>
       <c r="E61" t="n">
-        <v>1246.821889346108</v>
+        <v>1250.601363158063</v>
       </c>
     </row>
     <row r="62">
@@ -5241,10 +5241,10 @@
         <v>1082.536474524743</v>
       </c>
       <c r="D62" t="n">
-        <v>976.1230061703427</v>
+        <v>974.9289669300528</v>
       </c>
       <c r="E62" t="n">
-        <v>1184.639280434673</v>
+        <v>1187.261187720775</v>
       </c>
     </row>
     <row r="63">
@@ -5258,10 +5258,10 @@
         <v>1009.249600152956</v>
       </c>
       <c r="D63" t="n">
-        <v>903.8167351592994</v>
+        <v>891.9099079055846</v>
       </c>
       <c r="E63" t="n">
-        <v>1126.767977411633</v>
+        <v>1116.076412785387</v>
       </c>
     </row>
     <row r="64">
@@ -5275,10 +5275,10 @@
         <v>965.1000024269335</v>
       </c>
       <c r="D64" t="n">
-        <v>861.5769884435613</v>
+        <v>850.3303393912894</v>
       </c>
       <c r="E64" t="n">
-        <v>1071.875543440956</v>
+        <v>1074.466713152407</v>
       </c>
     </row>
     <row r="65">
@@ -5292,10 +5292,10 @@
         <v>976.67595209551</v>
       </c>
       <c r="D65" t="n">
-        <v>869.356368145471</v>
+        <v>858.7184099774719</v>
       </c>
       <c r="E65" t="n">
-        <v>1081.251390989735</v>
+        <v>1091.508811698491</v>
       </c>
     </row>
     <row r="66">
@@ -5309,10 +5309,10 @@
         <v>1047.103098959616</v>
       </c>
       <c r="D66" t="n">
-        <v>935.509719230779</v>
+        <v>936.3577726294488</v>
       </c>
       <c r="E66" t="n">
-        <v>1163.595431363017</v>
+        <v>1158.507412171739</v>
       </c>
     </row>
     <row r="67">
@@ -5326,10 +5326,10 @@
         <v>1115.884027724745</v>
       </c>
       <c r="D67" t="n">
-        <v>1002.936174593469</v>
+        <v>993.4862799757075</v>
       </c>
       <c r="E67" t="n">
-        <v>1226.642392275384</v>
+        <v>1225.218587419654</v>
       </c>
     </row>
     <row r="68">
@@ -5343,10 +5343,10 @@
         <v>1148.152380722494</v>
       </c>
       <c r="D68" t="n">
-        <v>1034.767155941059</v>
+        <v>1035.379100853106</v>
       </c>
       <c r="E68" t="n">
-        <v>1262.957178400572</v>
+        <v>1264.679218066692</v>
       </c>
     </row>
     <row r="69">
@@ -5360,10 +5360,10 @@
         <v>1090.175834435503</v>
       </c>
       <c r="D69" t="n">
-        <v>973.8160863523747</v>
+        <v>976.6144726201186</v>
       </c>
       <c r="E69" t="n">
-        <v>1214.70352229236</v>
+        <v>1208.94286088568</v>
       </c>
     </row>
     <row r="70">
@@ -5377,10 +5377,10 @@
         <v>1016.771668195333</v>
       </c>
       <c r="D70" t="n">
-        <v>900.1539143319843</v>
+        <v>898.500670655127</v>
       </c>
       <c r="E70" t="n">
-        <v>1136.457005064831</v>
+        <v>1129.36325420224</v>
       </c>
     </row>
     <row r="71">
@@ -5394,10 +5394,10 @@
         <v>972.5634245347966</v>
       </c>
       <c r="D71" t="n">
-        <v>863.2267085722405</v>
+        <v>851.1106636073009</v>
       </c>
       <c r="E71" t="n">
-        <v>1098.95247140279</v>
+        <v>1100.584188061614</v>
       </c>
     </row>
     <row r="72">
@@ -5411,10 +5411,10 @@
         <v>984.0220823347993</v>
       </c>
       <c r="D72" t="n">
-        <v>873.5396712854207</v>
+        <v>857.7172416401791</v>
       </c>
       <c r="E72" t="n">
-        <v>1104.40494927799</v>
+        <v>1099.162966470929</v>
       </c>
     </row>
     <row r="73">
@@ -5428,10 +5428,10 @@
         <v>1054.331937330272</v>
       </c>
       <c r="D73" t="n">
-        <v>937.4738643760735</v>
+        <v>934.4023220877197</v>
       </c>
       <c r="E73" t="n">
-        <v>1177.791031169795</v>
+        <v>1183.228091036189</v>
       </c>
     </row>
     <row r="74">
@@ -5445,10 +5445,10 @@
         <v>1122.936928292453</v>
       </c>
       <c r="D74" t="n">
-        <v>999.9158096191394</v>
+        <v>992.600453287136</v>
       </c>
       <c r="E74" t="n">
-        <v>1245.215043145884</v>
+        <v>1240.230792874075</v>
       </c>
     </row>
     <row r="75">
@@ -5462,10 +5462,10 @@
         <v>1341.093612745986</v>
       </c>
       <c r="D75" t="n">
-        <v>1218.388378968127</v>
+        <v>1214.807385464609</v>
       </c>
       <c r="E75" t="n">
-        <v>1469.325420776817</v>
+        <v>1467.301945124871</v>
       </c>
     </row>
     <row r="76">
@@ -5479,10 +5479,10 @@
         <v>1282.941128655943</v>
       </c>
       <c r="D76" t="n">
-        <v>1158.748858015083</v>
+        <v>1152.15903138281</v>
       </c>
       <c r="E76" t="n">
-        <v>1411.522762363374</v>
+        <v>1403.259408257805</v>
       </c>
     </row>
     <row r="77">
@@ -5496,10 +5496,10 @@
         <v>1023.355401288453</v>
       </c>
       <c r="D77" t="n">
-        <v>894.6893786852063</v>
+        <v>902.836567057708</v>
       </c>
       <c r="E77" t="n">
-        <v>1149.105109473456</v>
+        <v>1151.368346779799</v>
       </c>
     </row>
     <row r="78">
@@ -5513,10 +5513,10 @@
         <v>1164.976843149366</v>
       </c>
       <c r="D78" t="n">
-        <v>1035.26137434525</v>
+        <v>1034.773681050646</v>
       </c>
       <c r="E78" t="n">
-        <v>1300.202963787241</v>
+        <v>1293.253790564426</v>
       </c>
     </row>
     <row r="79">
@@ -5530,10 +5530,10 @@
         <v>990.1952938877703</v>
       </c>
       <c r="D79" t="n">
-        <v>864.4977370994291</v>
+        <v>855.9829700672524</v>
       </c>
       <c r="E79" t="n">
-        <v>1124.147087367773</v>
+        <v>1131.044063159306</v>
       </c>
     </row>
     <row r="80">
@@ -5547,10 +5547,10 @@
         <v>1060.329211080336</v>
       </c>
       <c r="D80" t="n">
-        <v>927.0893951248154</v>
+        <v>927.5746454015626</v>
       </c>
       <c r="E80" t="n">
-        <v>1187.910626438641</v>
+        <v>1192.232615798937</v>
       </c>
     </row>
     <row r="81">
@@ -5564,10 +5564,10 @@
         <v>1128.69961830524</v>
       </c>
       <c r="D81" t="n">
-        <v>999.327285689087</v>
+        <v>997.7072548617065</v>
       </c>
       <c r="E81" t="n">
-        <v>1258.234992710356</v>
+        <v>1266.734665140249</v>
       </c>
     </row>
     <row r="82">
@@ -5581,10 +5581,10 @@
         <v>1160.557449762741</v>
       </c>
       <c r="D82" t="n">
-        <v>1021.993500773011</v>
+        <v>1023.916240598587</v>
       </c>
       <c r="E82" t="n">
-        <v>1290.986610134912</v>
+        <v>1291.156444634174</v>
       </c>
     </row>
     <row r="83">
@@ -5598,10 +5598,10 @@
         <v>1102.111736001067</v>
       </c>
       <c r="D83" t="n">
-        <v>960.3857516685689</v>
+        <v>954.4198515733999</v>
       </c>
       <c r="E83" t="n">
-        <v>1235.259924218673</v>
+        <v>1232.597939092382</v>
       </c>
     </row>
     <row r="84">
@@ -5615,10 +5615,10 @@
         <v>1028.297048220734</v>
       </c>
       <c r="D84" t="n">
-        <v>895.2824932766662</v>
+        <v>887.277952942661</v>
       </c>
       <c r="E84" t="n">
-        <v>1169.63662284041</v>
+        <v>1167.612444913092</v>
       </c>
     </row>
     <row r="85">
@@ -5632,10 +5632,10 @@
         <v>983.6196370857267</v>
       </c>
       <c r="D85" t="n">
-        <v>839.8277401430992</v>
+        <v>834.2410809457058</v>
       </c>
       <c r="E85" t="n">
-        <v>1123.009917803374</v>
+        <v>1124.977220242725</v>
       </c>
     </row>
     <row r="86">
@@ -5649,10 +5649,10 @@
         <v>994.550481476819</v>
       </c>
       <c r="D86" t="n">
-        <v>854.1907162388516</v>
+        <v>855.241954759833</v>
       </c>
       <c r="E86" t="n">
-        <v>1144.31289861656</v>
+        <v>1126.608107745042</v>
       </c>
     </row>
     <row r="87">
@@ -5666,10 +5666,10 @@
         <v>1064.391168997712</v>
       </c>
       <c r="D87" t="n">
-        <v>917.545984674467</v>
+        <v>927.4343621573069</v>
       </c>
       <c r="E87" t="n">
-        <v>1207.639414122717</v>
+        <v>1216.767693054387</v>
       </c>
     </row>
     <row r="88">
@@ -5683,10 +5683,10 @@
         <v>1132.409700617017</v>
       </c>
       <c r="D88" t="n">
-        <v>989.0000252507294</v>
+        <v>991.6104239187215</v>
       </c>
       <c r="E88" t="n">
-        <v>1280.980547158729</v>
+        <v>1282.086192019623</v>
       </c>
     </row>
     <row r="89">
@@ -5700,10 +5700,10 @@
         <v>1163.974302402895</v>
       </c>
       <c r="D89" t="n">
-        <v>1014.412444290999</v>
+        <v>1005.097175851256</v>
       </c>
       <c r="E89" t="n">
-        <v>1317.527767452701</v>
+        <v>1320.454773860611</v>
       </c>
     </row>
     <row r="90">
@@ -5717,10 +5717,10 @@
         <v>1105.2353589696</v>
       </c>
       <c r="D90" t="n">
-        <v>953.7708161490617</v>
+        <v>951.7955129748964</v>
       </c>
       <c r="E90" t="n">
-        <v>1251.660543600414</v>
+        <v>1255.326728183173</v>
       </c>
     </row>
     <row r="91">
@@ -5734,10 +5734,10 @@
         <v>1031.127441517968</v>
       </c>
       <c r="D91" t="n">
-        <v>878.9173145660484</v>
+        <v>873.1856206250393</v>
       </c>
       <c r="E91" t="n">
-        <v>1181.40249618688</v>
+        <v>1183.44518235281</v>
       </c>
     </row>
     <row r="92">
@@ -5751,10 +5751,10 @@
         <v>1172.103778101246</v>
       </c>
       <c r="D92" t="n">
-        <v>1026.181089170513</v>
+        <v>1023.894367031598</v>
       </c>
       <c r="E92" t="n">
-        <v>1309.917443428695</v>
+        <v>1333.82297342896</v>
       </c>
     </row>
     <row r="93">
@@ -5768,10 +5768,10 @@
         <v>1182.741392820795</v>
       </c>
       <c r="D93" t="n">
-        <v>1022.0404663896</v>
+        <v>1021.612244608349</v>
       </c>
       <c r="E93" t="n">
-        <v>1330.80812388413</v>
+        <v>1350.239362950621</v>
       </c>
     </row>
     <row r="94">
@@ -5785,10 +5785,10 @@
         <v>1066.165935477106</v>
       </c>
       <c r="D94" t="n">
-        <v>916.1573750227896</v>
+        <v>895.2959160020431</v>
       </c>
       <c r="E94" t="n">
-        <v>1222.726085674385</v>
+        <v>1228.18168726087</v>
       </c>
     </row>
     <row r="95">
@@ -5802,10 +5802,10 @@
         <v>1133.891237424835</v>
       </c>
       <c r="D95" t="n">
-        <v>963.7477046812076</v>
+        <v>970.7921033025937</v>
       </c>
       <c r="E95" t="n">
-        <v>1289.621912769619</v>
+        <v>1295.02769145852</v>
       </c>
     </row>
     <row r="96">
@@ -5819,10 +5819,10 @@
         <v>1165.103963604767</v>
       </c>
       <c r="D96" t="n">
-        <v>1006.245277144244</v>
+        <v>997.2563023808781</v>
       </c>
       <c r="E96" t="n">
-        <v>1321.429776240731</v>
+        <v>1325.164184340756</v>
       </c>
     </row>
     <row r="97">
@@ -5836,10 +5836,10 @@
         <v>1106.071790500176</v>
       </c>
       <c r="D97" t="n">
-        <v>955.0954619738309</v>
+        <v>932.8696778381927</v>
       </c>
       <c r="E97" t="n">
-        <v>1262.84958286456</v>
+        <v>1275.019208769167</v>
       </c>
     </row>
     <row r="98">
@@ -5853,10 +5853,10 @@
         <v>1031.553351508023</v>
       </c>
       <c r="D98" t="n">
-        <v>870.8865567693556</v>
+        <v>855.3079266282776</v>
       </c>
       <c r="E98" t="n">
-        <v>1191.323189647729</v>
+        <v>1189.586556901426</v>
       </c>
     </row>
     <row r="99">
@@ -5870,10 +5870,10 @@
         <v>986.2308350953491</v>
       </c>
       <c r="D99" t="n">
-        <v>814.6451500810061</v>
+        <v>816.5207296116996</v>
       </c>
       <c r="E99" t="n">
-        <v>1148.660970295241</v>
+        <v>1152.326708039396</v>
       </c>
     </row>
     <row r="100">
@@ -5887,10 +5887,10 @@
         <v>996.5165742090961</v>
       </c>
       <c r="D100" t="n">
-        <v>828.6828722564476</v>
+        <v>810.4564509712344</v>
       </c>
       <c r="E100" t="n">
-        <v>1164.09300204838</v>
+        <v>1173.347854347575</v>
       </c>
     </row>
     <row r="101">
@@ -5904,10 +5904,10 @@
         <v>1065.653510518246</v>
       </c>
       <c r="D101" t="n">
-        <v>892.4331594142777</v>
+        <v>882.8874888715917</v>
       </c>
       <c r="E101" t="n">
-        <v>1230.425451780778</v>
+        <v>1237.701273505516</v>
       </c>
     </row>
     <row r="102">
@@ -5921,10 +5921,10 @@
         <v>1319.091206118543</v>
       </c>
       <c r="D102" t="n">
-        <v>1148.040096651841</v>
+        <v>1145.203188662355</v>
       </c>
       <c r="E102" t="n">
-        <v>1476.913726543638</v>
+        <v>1502.757350618408</v>
       </c>
     </row>
     <row r="103">
@@ -5938,10 +5938,10 @@
         <v>1164.005079302683</v>
       </c>
       <c r="D103" t="n">
-        <v>978.0104462740429</v>
+        <v>985.4039437578018</v>
       </c>
       <c r="E103" t="n">
-        <v>1341.510033636453</v>
+        <v>1345.483009092918</v>
       </c>
     </row>
     <row r="104">
@@ -5955,10 +5955,10 @@
         <v>1104.621030592168</v>
       </c>
       <c r="D104" t="n">
-        <v>927.7403370552032</v>
+        <v>930.1325165132439</v>
       </c>
       <c r="E104" t="n">
-        <v>1282.379708908793</v>
+        <v>1281.093409880161</v>
       </c>
     </row>
     <row r="105">
@@ -5972,10 +5972,10 @@
         <v>1029.809361928465</v>
       </c>
       <c r="D105" t="n">
-        <v>851.4567152026481</v>
+        <v>837.8295087022329</v>
       </c>
       <c r="E105" t="n">
-        <v>1206.467360631531</v>
+        <v>1211.412993933751</v>
       </c>
     </row>
     <row r="106">
@@ -5989,10 +5989,10 @@
         <v>984.1936158442409</v>
       </c>
       <c r="D106" t="n">
-        <v>804.9073939313573</v>
+        <v>791.8612453039614</v>
       </c>
       <c r="E106" t="n">
-        <v>1168.863139209431</v>
+        <v>1170.775585154724</v>
       </c>
     </row>
     <row r="107">
@@ -6006,10 +6006,10 @@
         <v>1180.191748610845</v>
       </c>
       <c r="D107" t="n">
-        <v>1007.949538991932</v>
+        <v>1000.310069450239</v>
       </c>
       <c r="E107" t="n">
-        <v>1356.816022210056</v>
+        <v>1364.317093025794</v>
       </c>
     </row>
     <row r="108">
@@ -6023,10 +6023,10 @@
         <v>1063.088477858374</v>
       </c>
       <c r="D108" t="n">
-        <v>881.3422865160883</v>
+        <v>877.7244036841414</v>
       </c>
       <c r="E108" t="n">
-        <v>1251.063074710343</v>
+        <v>1252.835492062956</v>
       </c>
     </row>
     <row r="109">
@@ -6040,10 +6040,10 @@
         <v>1130.227320462678</v>
       </c>
       <c r="D109" t="n">
-        <v>938.7893922833379</v>
+        <v>941.585293426625</v>
       </c>
       <c r="E109" t="n">
-        <v>1322.530710231747</v>
+        <v>1311.552503355839</v>
       </c>
     </row>
     <row r="110">
@@ -6057,10 +6057,10 @@
         <v>1160.853587299597</v>
       </c>
       <c r="D110" t="n">
-        <v>964.962430053847</v>
+        <v>954.0993217292934</v>
       </c>
       <c r="E110" t="n">
-        <v>1349.888393406849</v>
+        <v>1355.473334191048</v>
       </c>
     </row>
     <row r="111">
@@ -6074,10 +6074,10 @@
         <v>1101.234954851776</v>
       </c>
       <c r="D111" t="n">
-        <v>917.2874973089034</v>
+        <v>907.2312667427298</v>
       </c>
       <c r="E111" t="n">
-        <v>1288.310583744975</v>
+        <v>1300.558470863731</v>
       </c>
     </row>
     <row r="112">
@@ -6091,10 +6091,10 @@
         <v>1026.247348385124</v>
       </c>
       <c r="D112" t="n">
-        <v>843.1468805470344</v>
+        <v>818.6562352703803</v>
       </c>
       <c r="E112" t="n">
-        <v>1205.34040249053</v>
+        <v>1221.427733129506</v>
       </c>
     </row>
     <row r="113">
@@ -6108,10 +6108,10 @@
         <v>980.3970185637604</v>
       </c>
       <c r="D113" t="n">
-        <v>782.1263318687799</v>
+        <v>772.8055435883639</v>
       </c>
       <c r="E113" t="n">
-        <v>1157.139390772069</v>
+        <v>1180.192332750836</v>
       </c>
     </row>
     <row r="114">
@@ -6125,10 +6125,10 @@
         <v>990.2135902027896</v>
       </c>
       <c r="D114" t="n">
-        <v>793.5186116568319</v>
+        <v>784.7381024537667</v>
       </c>
       <c r="E114" t="n">
-        <v>1173.342958820073</v>
+        <v>1191.930987976397</v>
       </c>
     </row>
     <row r="115">
@@ -6142,10 +6142,10 @@
         <v>1058.94000497199</v>
       </c>
       <c r="D115" t="n">
-        <v>862.6733709318022</v>
+        <v>851.0703673969356</v>
       </c>
       <c r="E115" t="n">
-        <v>1246.08940320083</v>
+        <v>1276.158578282421</v>
       </c>
     </row>
     <row r="116">
@@ -6159,10 +6159,10 @@
         <v>1125.90290977335</v>
       </c>
       <c r="D116" t="n">
-        <v>922.6470862732086</v>
+        <v>909.1122090177269</v>
       </c>
       <c r="E116" t="n">
-        <v>1328.068572235796</v>
+        <v>1323.61369389873</v>
       </c>
     </row>
     <row r="117">
@@ -6176,10 +6176,10 @@
         <v>1156.411884741579</v>
       </c>
       <c r="D117" t="n">
-        <v>948.5500432690237</v>
+        <v>950.3689455410713</v>
       </c>
       <c r="E117" t="n">
-        <v>1345.119177095518</v>
+        <v>1361.208488021547</v>
       </c>
     </row>
     <row r="118">
@@ -6193,10 +6193,10 @@
         <v>1096.617314491091</v>
       </c>
       <c r="D118" t="n">
-        <v>887.3176107829386</v>
+        <v>875.490991788459</v>
       </c>
       <c r="E118" t="n">
-        <v>1288.476811488336</v>
+        <v>1311.080541319013</v>
       </c>
     </row>
     <row r="119">
@@ -6210,10 +6210,10 @@
         <v>1021.512416155491</v>
       </c>
       <c r="D119" t="n">
-        <v>816.0025361940633</v>
+        <v>795.8246379028662</v>
       </c>
       <c r="E119" t="n">
-        <v>1239.585821985926</v>
+        <v>1240.742595551385</v>
       </c>
     </row>
     <row r="120">
@@ -6227,10 +6227,10 @@
         <v>975.5447944655496</v>
       </c>
       <c r="D120" t="n">
-        <v>761.7206077511682</v>
+        <v>753.5621645141554</v>
       </c>
       <c r="E120" t="n">
-        <v>1175.478222703121</v>
+        <v>1189.069921791905</v>
       </c>
     </row>
     <row r="121">
@@ -6244,10 +6244,10 @@
         <v>985.30272017032</v>
       </c>
       <c r="D121" t="n">
-        <v>769.5588267675495</v>
+        <v>746.1856993651908</v>
       </c>
       <c r="E121" t="n">
-        <v>1181.614544839771</v>
+        <v>1206.316941989214</v>
       </c>
     </row>
     <row r="122">
@@ -6261,10 +6261,10 @@
         <v>1239.917466395302</v>
       </c>
       <c r="D122" t="n">
-        <v>1017.229741800785</v>
+        <v>1005.998885098249</v>
       </c>
       <c r="E122" t="n">
-        <v>1451.086875432298</v>
+        <v>1463.36104819763</v>
       </c>
     </row>
     <row r="123">
@@ -6278,10 +6278,10 @@
         <v>1120.816101937929</v>
       </c>
       <c r="D123" t="n">
-        <v>893.2291498667921</v>
+        <v>878.0187506355413</v>
       </c>
       <c r="E123" t="n">
-        <v>1338.236250555834</v>
+        <v>1338.846503980354</v>
       </c>
     </row>
     <row r="124">
@@ -6295,10 +6295,10 @@
         <v>1151.325076906171</v>
       </c>
       <c r="D124" t="n">
-        <v>939.0699333527426</v>
+        <v>916.28498307452</v>
       </c>
       <c r="E124" t="n">
-        <v>1371.876779975932</v>
+        <v>1383.48661520065</v>
       </c>
     </row>
     <row r="125">
@@ -6312,10 +6312,10 @@
         <v>1091.530506655575</v>
       </c>
       <c r="D125" t="n">
-        <v>882.5847491531239</v>
+        <v>860.070322782914</v>
       </c>
       <c r="E125" t="n">
-        <v>1312.639472956311</v>
+        <v>1307.360054125079</v>
       </c>
     </row>
     <row r="126">
@@ -6329,10 +6329,10 @@
         <v>1016.425608319998</v>
       </c>
       <c r="D126" t="n">
-        <v>793.6010842736123</v>
+        <v>791.8198359868353</v>
       </c>
       <c r="E126" t="n">
-        <v>1228.387091392458</v>
+        <v>1251.225480395819</v>
       </c>
     </row>
     <row r="127">
@@ -6346,10 +6346,10 @@
         <v>970.4579866300505</v>
       </c>
       <c r="D127" t="n">
-        <v>734.2956522446424</v>
+        <v>748.8760482693117</v>
       </c>
       <c r="E127" t="n">
-        <v>1189.501132001599</v>
+        <v>1201.803690339604</v>
       </c>
     </row>
     <row r="128">
@@ -6363,10 +6363,10 @@
         <v>980.2159123348806</v>
       </c>
       <c r="D128" t="n">
-        <v>739.475182874328</v>
+        <v>749.1934067399295</v>
       </c>
       <c r="E128" t="n">
-        <v>1193.749612663619</v>
+        <v>1201.492012238898</v>
       </c>
     </row>
     <row r="129">
@@ -6380,10 +6380,10 @@
         <v>1048.883681169494</v>
       </c>
       <c r="D129" t="n">
-        <v>810.7699967989029</v>
+        <v>797.0940514056861</v>
       </c>
       <c r="E129" t="n">
-        <v>1280.622998077173</v>
+        <v>1286.111653664537</v>
       </c>
     </row>
     <row r="130">
@@ -6397,10 +6397,10 @@
         <v>1115.905231905452</v>
       </c>
       <c r="D130" t="n">
-        <v>880.6226112828475</v>
+        <v>874.2138139572742</v>
       </c>
       <c r="E130" t="n">
-        <v>1352.401583606892</v>
+        <v>1360.700245822982</v>
       </c>
     </row>
     <row r="131">
@@ -6414,10 +6414,10 @@
         <v>1146.47285280795</v>
       </c>
       <c r="D131" t="n">
-        <v>906.6021653876461</v>
+        <v>895.9774011416586</v>
       </c>
       <c r="E131" t="n">
-        <v>1367.061016191345</v>
+        <v>1399.008877440329</v>
       </c>
     </row>
     <row r="132">
@@ -6431,10 +6431,10 @@
         <v>1086.795574425925</v>
       </c>
       <c r="D132" t="n">
-        <v>840.6098381343265</v>
+        <v>834.9883933906825</v>
       </c>
       <c r="E132" t="n">
-        <v>1329.047939406215</v>
+        <v>1337.05750974819</v>
       </c>
     </row>
     <row r="133">
@@ -6448,10 +6448,10 @@
         <v>1011.807967958994</v>
       </c>
       <c r="D133" t="n">
-        <v>769.0671547535536</v>
+        <v>763.2575271272685</v>
       </c>
       <c r="E133" t="n">
-        <v>1246.359576589625</v>
+        <v>1248.724959096469</v>
       </c>
     </row>
     <row r="134">
@@ -6465,10 +6465,10 @@
         <v>966.0162840720424</v>
       </c>
       <c r="D134" t="n">
-        <v>726.3284103077078</v>
+        <v>708.5162524475783</v>
       </c>
       <c r="E134" t="n">
-        <v>1192.702472701447</v>
+        <v>1213.038437778012</v>
       </c>
     </row>
     <row r="135">
@@ -6482,10 +6482,10 @@
         <v>975.8915016455321</v>
       </c>
       <c r="D135" t="n">
-        <v>742.4626554119145</v>
+        <v>723.0018073617072</v>
       </c>
       <c r="E135" t="n">
-        <v>1213.024900509869</v>
+        <v>1240.630533418107</v>
       </c>
     </row>
     <row r="136">
@@ -6499,10 +6499,10 @@
         <v>1044.735208283126</v>
       </c>
       <c r="D136" t="n">
-        <v>792.2500974797331</v>
+        <v>790.6507235867361</v>
       </c>
       <c r="E136" t="n">
-        <v>1298.68332362575</v>
+        <v>1293.286819666141</v>
       </c>
     </row>
     <row r="137">
@@ -6516,10 +6516,10 @@
         <v>1111.932696822012</v>
       </c>
       <c r="D137" t="n">
-        <v>869.4262311923756</v>
+        <v>849.5103458046676</v>
       </c>
       <c r="E137" t="n">
-        <v>1361.841664934353</v>
+        <v>1366.995424591764</v>
       </c>
     </row>
     <row r="138">
@@ -6533,10 +6533,10 @@
         <v>1142.676255527393</v>
       </c>
       <c r="D138" t="n">
-        <v>893.2426224464602</v>
+        <v>869.1115792993352</v>
       </c>
       <c r="E138" t="n">
-        <v>1386.631596702026</v>
+        <v>1409.288963163173</v>
       </c>
     </row>
     <row r="139">
@@ -6550,10 +6550,10 @@
         <v>1083.23356088259</v>
       </c>
       <c r="D139" t="n">
-        <v>817.5985583468613</v>
+        <v>800.4346739882216</v>
       </c>
       <c r="E139" t="n">
-        <v>1329.146307763311</v>
+        <v>1361.322551408146</v>
       </c>
     </row>
     <row r="140">
@@ -6567,10 +6567,10 @@
         <v>1008.421892218877</v>
       </c>
       <c r="D140" t="n">
-        <v>751.7615166087501</v>
+        <v>735.0319917770053</v>
       </c>
       <c r="E140" t="n">
-        <v>1248.327060581141</v>
+        <v>1276.50194301883</v>
       </c>
     </row>
     <row r="141">
@@ -6584,10 +6584,10 @@
         <v>962.864792068956</v>
       </c>
       <c r="D141" t="n">
-        <v>708.8641127454024</v>
+        <v>691.8573608842371</v>
       </c>
       <c r="E141" t="n">
-        <v>1215.547207898775</v>
+        <v>1228.707880848473</v>
       </c>
     </row>
     <row r="142">
@@ -6601,10 +6601,10 @@
         <v>973.0332393140745</v>
       </c>
       <c r="D142" t="n">
-        <v>705.5211152950749</v>
+        <v>699.5276540007086</v>
       </c>
       <c r="E142" t="n">
-        <v>1225.9947857243</v>
+        <v>1247.250879943882</v>
       </c>
     </row>
     <row r="143">
@@ -6618,10 +6618,10 @@
         <v>1042.170175623237</v>
       </c>
       <c r="D143" t="n">
-        <v>780.5207194194011</v>
+        <v>764.9787319132134</v>
       </c>
       <c r="E143" t="n">
-        <v>1308.157527672018</v>
+        <v>1330.07397177461</v>
       </c>
     </row>
     <row r="144">
@@ -6635,10 +6635,10 @@
         <v>1109.602247899379</v>
       </c>
       <c r="D144" t="n">
-        <v>842.4252950714101</v>
+        <v>826.6897380114734</v>
       </c>
       <c r="E144" t="n">
-        <v>1370.622461115975</v>
+        <v>1377.414284249089</v>
       </c>
     </row>
     <row r="145">
@@ -6652,10 +6652,10 @@
         <v>1140.639036276346</v>
       </c>
       <c r="D145" t="n">
-        <v>872.1998485370764</v>
+        <v>847.4701671319175</v>
       </c>
       <c r="E145" t="n">
-        <v>1395.81031244999</v>
+        <v>1421.879036417431</v>
       </c>
     </row>
     <row r="146">
@@ -6669,10 +6669,10 @@
         <v>1081.489571303008</v>
       </c>
       <c r="D146" t="n">
-        <v>810.475152707391</v>
+        <v>791.400127507282</v>
       </c>
       <c r="E146" t="n">
-        <v>1344.37939131423</v>
+        <v>1367.927207947912</v>
       </c>
     </row>
     <row r="147">
@@ -6686,10 +6686,10 @@
         <v>1006.971132310863</v>
       </c>
       <c r="D147" t="n">
-        <v>717.5966773974243</v>
+        <v>717.4129383393191</v>
       </c>
       <c r="E147" t="n">
-        <v>1283.98219243713</v>
+        <v>1294.628916186807</v>
       </c>
     </row>
     <row r="148">
@@ -6703,10 +6703,10 @@
         <v>961.7659077669487</v>
       </c>
       <c r="D148" t="n">
-        <v>682.9126210036769</v>
+        <v>674.8853984675183</v>
       </c>
       <c r="E148" t="n">
-        <v>1230.551119331713</v>
+        <v>1245.327916220252</v>
       </c>
     </row>
     <row r="149">
@@ -6720,10 +6720,10 @@
         <v>972.2275846836039</v>
       </c>
       <c r="D149" t="n">
-        <v>697.3035251999322</v>
+        <v>663.5820747200023</v>
       </c>
       <c r="E149" t="n">
-        <v>1250.912252273799</v>
+        <v>1262.163221000663</v>
       </c>
     </row>
     <row r="150">
@@ -6737,10 +6737,10 @@
         <v>1041.657750664377</v>
       </c>
       <c r="D150" t="n">
-        <v>759.2711854409428</v>
+        <v>746.6648560045647</v>
       </c>
       <c r="E150" t="n">
-        <v>1303.695766472391</v>
+        <v>1345.770928141352</v>
       </c>
     </row>
     <row r="151">
@@ -6754,10 +6754,10 @@
         <v>1109.383052611833</v>
       </c>
       <c r="D151" t="n">
-        <v>823.8459144968436</v>
+        <v>796.5178556458141</v>
       </c>
       <c r="E151" t="n">
-        <v>1384.281459931375</v>
+        <v>1425.023349082422</v>
       </c>
     </row>
     <row r="152">
@@ -6771,10 +6771,10 @@
         <v>1140.77171659487</v>
       </c>
       <c r="D152" t="n">
-        <v>850.9616768892622</v>
+        <v>827.4890930278578</v>
       </c>
       <c r="E152" t="n">
-        <v>1416.582521354846</v>
+        <v>1446.007730900039</v>
       </c>
     </row>
     <row r="153">
@@ -6788,10 +6788,10 @@
         <v>1267.921104617446</v>
       </c>
       <c r="D153" t="n">
-        <v>962.5670985086215</v>
+        <v>971.6852633228635</v>
       </c>
       <c r="E153" t="n">
-        <v>1546.130512508438</v>
+        <v>1570.828913374063</v>
       </c>
     </row>
     <row r="154">
@@ -6805,10 +6805,10 @@
         <v>1007.807563841149</v>
       </c>
       <c r="D154" t="n">
-        <v>722.1903633377709</v>
+        <v>690.5499433349711</v>
       </c>
       <c r="E154" t="n">
-        <v>1304.239377240563</v>
+        <v>1317.196024820517</v>
       </c>
     </row>
     <row r="155">
@@ -6822,10 +6822,10 @@
         <v>962.8955689688307</v>
       </c>
       <c r="D155" t="n">
-        <v>677.279370316831</v>
+        <v>661.1390012672023</v>
       </c>
       <c r="E155" t="n">
-        <v>1255.326156268641</v>
+        <v>1247.412932747473</v>
       </c>
     </row>
     <row r="156">
@@ -6839,10 +6839,10 @@
         <v>973.7091214912355</v>
       </c>
       <c r="D156" t="n">
-        <v>680.2972020272097</v>
+        <v>665.7113364763893</v>
       </c>
       <c r="E156" t="n">
-        <v>1249.516205565438</v>
+        <v>1295.281310695245</v>
       </c>
     </row>
     <row r="157">
@@ -6856,10 +6856,10 @@
         <v>1043.432517143788</v>
       </c>
       <c r="D157" t="n">
-        <v>745.0478202692973</v>
+        <v>727.2985156386321</v>
       </c>
       <c r="E157" t="n">
-        <v>1348.635963125995</v>
+        <v>1349.962585805112</v>
       </c>
     </row>
     <row r="158">
@@ -6873,10 +6873,10 @@
         <v>1111.568340631427</v>
       </c>
       <c r="D158" t="n">
-        <v>808.9472933898751</v>
+        <v>787.4103305784339</v>
       </c>
       <c r="E158" t="n">
-        <v>1421.816998016239</v>
+        <v>1417.037482420865</v>
       </c>
     </row>
     <row r="159">
@@ -6890,10 +6890,10 @@
         <v>1143.250234285988</v>
       </c>
       <c r="D159" t="n">
-        <v>856.5321608573225</v>
+        <v>816.5472928530984</v>
       </c>
       <c r="E159" t="n">
-        <v>1440.962895552904</v>
+        <v>1476.955751015799</v>
       </c>
     </row>
     <row r="160">
@@ -6907,10 +6907,10 @@
         <v>1084.745874590006</v>
       </c>
       <c r="D160" t="n">
-        <v>767.613923847684</v>
+        <v>747.6192910804829</v>
       </c>
       <c r="E160" t="n">
-        <v>1390.962403316772</v>
+        <v>1405.686620010419</v>
       </c>
     </row>
     <row r="161">
@@ -6924,10 +6924,10 @@
         <v>1010.931186809677</v>
       </c>
       <c r="D161" t="n">
-        <v>704.7332118046698</v>
+        <v>684.2619621350365</v>
       </c>
       <c r="E161" t="n">
-        <v>1316.625267743354</v>
+        <v>1340.285697505082</v>
       </c>
     </row>
     <row r="162">
@@ -6941,10 +6941,10 @@
         <v>966.3124216089839</v>
       </c>
       <c r="D162" t="n">
-        <v>658.7322920186148</v>
+        <v>639.3139298828459</v>
       </c>
       <c r="E162" t="n">
-        <v>1277.107711544621</v>
+        <v>1300.859011825386</v>
       </c>
     </row>
     <row r="163">
@@ -6958,10 +6958,10 @@
         <v>977.4192038029917</v>
       </c>
       <c r="D163" t="n">
-        <v>661.2086214206008</v>
+        <v>624.9737996013796</v>
       </c>
       <c r="E163" t="n">
-        <v>1267.382353441092</v>
+        <v>1307.670472282942</v>
       </c>
     </row>
     <row r="164">
@@ -6975,10 +6975,10 @@
         <v>1047.494475061453</v>
       </c>
       <c r="D164" t="n">
-        <v>731.6912630103254</v>
+        <v>711.657466668189</v>
       </c>
       <c r="E164" t="n">
-        <v>1371.782702154978</v>
+        <v>1393.062430735303</v>
       </c>
     </row>
     <row r="165">
@@ -6992,10 +6992,10 @@
         <v>1115.923528220662</v>
       </c>
       <c r="D165" t="n">
-        <v>802.2823653578961</v>
+        <v>768.5785878668696</v>
       </c>
       <c r="E165" t="n">
-        <v>1433.522661543065</v>
+        <v>1457.977211862307</v>
       </c>
     </row>
     <row r="166">
@@ -7009,10 +7009,10 @@
         <v>1147.898651546739</v>
       </c>
       <c r="D166" t="n">
-        <v>820.5347534054979</v>
+        <v>803.9288824311337</v>
       </c>
       <c r="E166" t="n">
-        <v>1465.231897804575</v>
+        <v>1474.08882639088</v>
       </c>
     </row>
     <row r="167">
@@ -7026,10 +7026,10 @@
         <v>1089.687521522607</v>
       </c>
       <c r="D167" t="n">
-        <v>749.7695576572964</v>
+        <v>742.9746098493214</v>
       </c>
       <c r="E167" t="n">
-        <v>1401.948694784845</v>
+        <v>1427.065802354115</v>
       </c>
     </row>
     <row r="168">
@@ -7043,10 +7043,10 @@
         <v>1016.107417479217</v>
       </c>
       <c r="D168" t="n">
-        <v>681.2748123774212</v>
+        <v>645.5922477994924</v>
       </c>
       <c r="E168" t="n">
-        <v>1328.598427428857</v>
+        <v>1359.892862307501</v>
       </c>
     </row>
     <row r="169">
@@ -7060,10 +7060,10 @@
         <v>971.7818819501193</v>
       </c>
       <c r="D169" t="n">
-        <v>639.7892183064681</v>
+        <v>618.5558132833702</v>
       </c>
       <c r="E169" t="n">
-        <v>1296.656171155446</v>
+        <v>1334.485902889522</v>
       </c>
     </row>
     <row r="170">
@@ -7077,10 +7077,10 @@
         <v>983.1818938157858</v>
       </c>
       <c r="D170" t="n">
-        <v>654.9202245164498</v>
+        <v>627.5023372220879</v>
       </c>
       <c r="E170" t="n">
-        <v>1317.638547861235</v>
+        <v>1322.809707796349</v>
       </c>
     </row>
     <row r="171">
@@ -7094,10 +7094,10 @@
         <v>1053.491748811517</v>
       </c>
       <c r="D171" t="n">
-        <v>720.2755589859894</v>
+        <v>691.4215075877089</v>
       </c>
       <c r="E171" t="n">
-        <v>1378.162437508344</v>
+        <v>1389.669450961925</v>
       </c>
     </row>
     <row r="172">
@@ -7111,10 +7111,10 @@
         <v>1122.096739773411</v>
       </c>
       <c r="D172" t="n">
-        <v>804.5497415453673</v>
+        <v>749.4883014051823</v>
       </c>
       <c r="E172" t="n">
-        <v>1452.47934539319</v>
+        <v>1486.588297903377</v>
       </c>
     </row>
     <row r="173">
@@ -7128,10 +7128,10 @@
         <v>1154.306446836929</v>
       </c>
       <c r="D173" t="n">
-        <v>817.8868371098297</v>
+        <v>784.1203848700659</v>
       </c>
       <c r="E173" t="n">
-        <v>1484.068518646407</v>
+        <v>1524.775583353972</v>
       </c>
     </row>
     <row r="174">
@@ -7145,10 +7145,10 @@
         <v>1096.271254615703</v>
       </c>
       <c r="D174" t="n">
-        <v>738.5741288696582</v>
+        <v>723.125300103831</v>
       </c>
       <c r="E174" t="n">
-        <v>1428.146191927398</v>
+        <v>1455.373407626961</v>
       </c>
     </row>
     <row r="175">
@@ -7162,10 +7162,10 @@
         <v>1022.867088375531</v>
       </c>
       <c r="D175" t="n">
-        <v>690.9758394961967</v>
+        <v>664.8625038233484</v>
       </c>
       <c r="E175" t="n">
-        <v>1374.125776734428</v>
+        <v>1394.359734971952</v>
       </c>
     </row>
     <row r="176">
@@ -7179,10 +7179,10 @@
         <v>978.7174906491507</v>
       </c>
       <c r="D176" t="n">
-        <v>622.4713142117455</v>
+        <v>591.1139587535016</v>
       </c>
       <c r="E176" t="n">
-        <v>1305.370400786813</v>
+        <v>1365.088825821144</v>
       </c>
     </row>
     <row r="177">
@@ -7196,10 +7196,10 @@
         <v>990.2347943834764</v>
       </c>
       <c r="D177" t="n">
-        <v>637.7249930324989</v>
+        <v>598.0666050082499</v>
       </c>
       <c r="E177" t="n">
-        <v>1332.028078490408</v>
+        <v>1347.183133644541</v>
       </c>
     </row>
     <row r="178">
@@ -7213,10 +7213,10 @@
         <v>1060.720587181867</v>
       </c>
       <c r="D178" t="n">
-        <v>702.5181266280467</v>
+        <v>691.5769755183824</v>
       </c>
       <c r="E178" t="n">
-        <v>1410.788158173965</v>
+        <v>1437.499754087957</v>
       </c>
     </row>
     <row r="179">
@@ -7230,10 +7230,10 @@
         <v>1129.442870012693</v>
       </c>
       <c r="D179" t="n">
-        <v>775.0334887826784</v>
+        <v>750.5683268683765</v>
       </c>
       <c r="E179" t="n">
-        <v>1483.626354420215</v>
+        <v>1517.099521267511</v>
       </c>
     </row>
     <row r="180">
@@ -7247,10 +7247,10 @@
         <v>1161.769868944792</v>
       </c>
       <c r="D180" t="n">
-        <v>809.9152175805743</v>
+        <v>771.6545376784971</v>
       </c>
       <c r="E180" t="n">
-        <v>1518.640665162018</v>
+        <v>1549.683871776135</v>
       </c>
     </row>
     <row r="181">
@@ -7264,10 +7264,10 @@
         <v>1103.793322657813</v>
       </c>
       <c r="D181" t="n">
-        <v>739.3924397037185</v>
+        <v>702.0647016195377</v>
       </c>
       <c r="E181" t="n">
-        <v>1460.404031865644</v>
+        <v>1501.827724539122</v>
       </c>
     </row>
   </sheetData>
@@ -7314,10 +7314,10 @@
         <v>1246.970674985937</v>
       </c>
       <c r="C2" t="n">
-        <v>1173.96714573212</v>
+        <v>1173.122022495945</v>
       </c>
       <c r="D2" t="n">
-        <v>1319.772464848572</v>
+        <v>1319.242157496333</v>
       </c>
     </row>
     <row r="3">
@@ -7328,10 +7328,10 @@
         <v>1201.991386255396</v>
       </c>
       <c r="C3" t="n">
-        <v>1131.020134293387</v>
+        <v>1128.852193766751</v>
       </c>
       <c r="D3" t="n">
-        <v>1277.630964717153</v>
+        <v>1280.674884383769</v>
       </c>
     </row>
     <row r="4">
@@ -7342,10 +7342,10 @@
         <v>1215.305547638776</v>
       </c>
       <c r="C4" t="n">
-        <v>1138.220099603731</v>
+        <v>1141.401421032581</v>
       </c>
       <c r="D4" t="n">
-        <v>1283.698709178859</v>
+        <v>1292.617377273831</v>
       </c>
     </row>
     <row r="5">
@@ -7356,10 +7356,10 @@
         <v>1281.341230069005</v>
       </c>
       <c r="C5" t="n">
-        <v>1207.660487990957</v>
+        <v>1206.70010906455</v>
       </c>
       <c r="D5" t="n">
-        <v>1357.333463334867</v>
+        <v>1356.488453663283</v>
       </c>
     </row>
     <row r="6">
@@ -7370,10 +7370,10 @@
         <v>1351.244598747907</v>
       </c>
       <c r="C6" t="n">
-        <v>1275.33500375675</v>
+        <v>1280.536603755604</v>
       </c>
       <c r="D6" t="n">
-        <v>1432.281008881259</v>
+        <v>1425.046457578179</v>
       </c>
     </row>
     <row r="7">
@@ -7384,10 +7384,10 @@
         <v>1379.918720901369</v>
       </c>
       <c r="C7" t="n">
-        <v>1304.493795544232</v>
+        <v>1306.597942429027</v>
       </c>
       <c r="D7" t="n">
-        <v>1457.818403275376</v>
+        <v>1454.238837431844</v>
       </c>
     </row>
     <row r="8">
@@ -7398,10 +7398,10 @@
         <v>1320.647955549118</v>
       </c>
       <c r="C8" t="n">
-        <v>1243.050476058343</v>
+        <v>1238.920980358062</v>
       </c>
       <c r="D8" t="n">
-        <v>1397.189233882481</v>
+        <v>1395.977353734972</v>
       </c>
     </row>
     <row r="9">
@@ -7412,10 +7412,10 @@
         <v>1242.182274513717</v>
       </c>
       <c r="C9" t="n">
-        <v>1168.16111715812</v>
+        <v>1170.611406393085</v>
       </c>
       <c r="D9" t="n">
-        <v>1317.065903145645</v>
+        <v>1319.55553304093</v>
       </c>
     </row>
     <row r="10">
@@ -7426,10 +7426,10 @@
         <v>1196.244908976352</v>
       </c>
       <c r="C10" t="n">
-        <v>1127.955626380057</v>
+        <v>1119.897080752128</v>
       </c>
       <c r="D10" t="n">
-        <v>1270.777619474838</v>
+        <v>1274.148777585703</v>
       </c>
     </row>
     <row r="11">
@@ -7440,10 +7440,10 @@
         <v>1208.453679339229</v>
       </c>
       <c r="C11" t="n">
-        <v>1132.525535956677</v>
+        <v>1134.073803124998</v>
       </c>
       <c r="D11" t="n">
-        <v>1283.180540931843</v>
+        <v>1283.909977551739</v>
       </c>
     </row>
     <row r="12">
@@ -7454,10 +7454,10 @@
         <v>1273.25750615065</v>
       </c>
       <c r="C12" t="n">
-        <v>1202.174139891811</v>
+        <v>1199.80797953972</v>
       </c>
       <c r="D12" t="n">
-        <v>1350.706178535284</v>
+        <v>1351.27222844328</v>
       </c>
     </row>
     <row r="13">
@@ -7468,10 +7468,10 @@
         <v>1341.826356255646</v>
       </c>
       <c r="C13" t="n">
-        <v>1263.829237846234</v>
+        <v>1267.010898099375</v>
       </c>
       <c r="D13" t="n">
-        <v>1421.889590587566</v>
+        <v>1413.05874579779</v>
       </c>
     </row>
     <row r="14">
@@ -7482,10 +7482,10 @@
         <v>1369.089482479666</v>
       </c>
       <c r="C14" t="n">
-        <v>1292.55652621646</v>
+        <v>1289.170462571542</v>
       </c>
       <c r="D14" t="n">
-        <v>1443.713641404715</v>
+        <v>1437.95146591192</v>
       </c>
     </row>
     <row r="15">
@@ -7496,10 +7496,10 @@
         <v>1308.3591880444</v>
       </c>
       <c r="C15" t="n">
-        <v>1228.721250522245</v>
+        <v>1233.026075320365</v>
       </c>
       <c r="D15" t="n">
-        <v>1376.290045243037</v>
+        <v>1380.76370200016</v>
       </c>
     </row>
     <row r="16">
@@ -7510,10 +7510,10 @@
         <v>1228.414481415777</v>
       </c>
       <c r="C16" t="n">
-        <v>1156.565393138869</v>
+        <v>1153.217723478678</v>
       </c>
       <c r="D16" t="n">
-        <v>1300.274852986691</v>
+        <v>1299.796731176451</v>
       </c>
     </row>
     <row r="17">
@@ -7524,10 +7524,10 @@
         <v>1181.008033353746</v>
       </c>
       <c r="C17" t="n">
-        <v>1106.200096295503</v>
+        <v>1102.891855211551</v>
       </c>
       <c r="D17" t="n">
-        <v>1258.416139987741</v>
+        <v>1254.468565225136</v>
       </c>
     </row>
     <row r="18">
@@ -7538,10 +7538,10 @@
         <v>1191.786811897225</v>
       </c>
       <c r="C18" t="n">
-        <v>1114.756600906988</v>
+        <v>1114.12851398366</v>
       </c>
       <c r="D18" t="n">
-        <v>1267.78878729217</v>
+        <v>1266.072724041917</v>
       </c>
     </row>
     <row r="19">
@@ -7552,10 +7552,10 @@
         <v>1255.227911019788</v>
       </c>
       <c r="C19" t="n">
-        <v>1175.683705777354</v>
+        <v>1182.673886514947</v>
       </c>
       <c r="D19" t="n">
-        <v>1326.979873811848</v>
+        <v>1328.713986647367</v>
       </c>
     </row>
     <row r="20">
@@ -7566,10 +7566,10 @@
         <v>1322.527844623886</v>
       </c>
       <c r="C20" t="n">
-        <v>1245.112591715059</v>
+        <v>1248.649648191194</v>
       </c>
       <c r="D20" t="n">
-        <v>1395.932197349177</v>
+        <v>1401.658292173384</v>
       </c>
     </row>
     <row r="21">
@@ -7580,10 +7580,10 @@
         <v>1348.640180718959</v>
       </c>
       <c r="C21" t="n">
-        <v>1272.864070435066</v>
+        <v>1272.103092955286</v>
       </c>
       <c r="D21" t="n">
-        <v>1423.925533129819</v>
+        <v>1424.792531845707</v>
       </c>
     </row>
     <row r="22">
@@ -7594,10 +7594,10 @@
         <v>1286.898762137486</v>
       </c>
       <c r="C22" t="n">
-        <v>1209.137929169168</v>
+        <v>1210.802174967813</v>
       </c>
       <c r="D22" t="n">
-        <v>1358.734541864942</v>
+        <v>1363.889743210821</v>
       </c>
     </row>
     <row r="23">
@@ -7608,10 +7608,10 @@
         <v>1206.100892814417</v>
       </c>
       <c r="C23" t="n">
-        <v>1130.200237333078</v>
+        <v>1130.16508976352</v>
       </c>
       <c r="D23" t="n">
-        <v>1283.498484657322</v>
+        <v>1285.35900175911</v>
       </c>
     </row>
     <row r="24">
@@ -7622,10 +7622,10 @@
         <v>1158.013912598774</v>
       </c>
       <c r="C24" t="n">
-        <v>1081.608950379064</v>
+        <v>1088.890090978334</v>
       </c>
       <c r="D24" t="n">
-        <v>1234.313550686468</v>
+        <v>1229.831038090871</v>
       </c>
     </row>
     <row r="25">
@@ -7636,10 +7636,10 @@
         <v>1168.295545062307</v>
       </c>
       <c r="C25" t="n">
-        <v>1092.212252382435</v>
+        <v>1091.765366066605</v>
       </c>
       <c r="D25" t="n">
-        <v>1239.878967245523</v>
+        <v>1243.896685454209</v>
       </c>
     </row>
     <row r="26">
@@ -7650,10 +7650,10 @@
         <v>1231.429540145661</v>
       </c>
       <c r="C26" t="n">
-        <v>1157.460718320553</v>
+        <v>1155.766371636552</v>
       </c>
       <c r="D26" t="n">
-        <v>1309.936830158423</v>
+        <v>1303.594292725748</v>
       </c>
     </row>
     <row r="27">
@@ -7664,10 +7664,10 @@
         <v>1298.614886597263</v>
       </c>
       <c r="C27" t="n">
-        <v>1221.600682635926</v>
+        <v>1221.778864677078</v>
       </c>
       <c r="D27" t="n">
-        <v>1374.510576905611</v>
+        <v>1373.502911182346</v>
       </c>
     </row>
     <row r="28">
@@ -7678,10 +7678,10 @@
         <v>1324.803469506447</v>
       </c>
       <c r="C28" t="n">
-        <v>1249.072544716817</v>
+        <v>1242.571275652108</v>
       </c>
       <c r="D28" t="n">
-        <v>1396.837068807525</v>
+        <v>1399.972903072593</v>
       </c>
     </row>
     <row r="29">
@@ -7692,10 +7692,10 @@
         <v>1263.323416896563</v>
       </c>
       <c r="C29" t="n">
-        <v>1190.710214597391</v>
+        <v>1187.81296943213</v>
       </c>
       <c r="D29" t="n">
-        <v>1343.51864862763</v>
+        <v>1338.191495615634</v>
       </c>
     </row>
     <row r="30">
@@ -7706,10 +7706,10 @@
         <v>1182.962509298936</v>
       </c>
       <c r="C30" t="n">
-        <v>1106.569022341175</v>
+        <v>1111.22190387846</v>
       </c>
       <c r="D30" t="n">
-        <v>1261.160405110909</v>
+        <v>1259.770194792478</v>
       </c>
     </row>
     <row r="31">
@@ -7720,10 +7720,10 @@
         <v>1135.475067616028</v>
       </c>
       <c r="C31" t="n">
-        <v>1063.671133921916</v>
+        <v>1058.624236097912</v>
       </c>
       <c r="D31" t="n">
-        <v>1210.088503526065</v>
+        <v>1207.407279858284</v>
       </c>
     </row>
   </sheetData>
@@ -7778,10 +7778,10 @@
         <v>959.0843825075809</v>
       </c>
       <c r="D2" t="n">
-        <v>885.0992600334203</v>
+        <v>884.6203258066329</v>
       </c>
       <c r="E2" t="n">
-        <v>1032.69984187357</v>
+        <v>1037.324625407874</v>
       </c>
     </row>
     <row r="3">
@@ -7795,10 +7795,10 @@
         <v>1030.041817892329</v>
       </c>
       <c r="D3" t="n">
-        <v>953.5503685410127</v>
+        <v>957.4126144887315</v>
       </c>
       <c r="E3" t="n">
-        <v>1104.670494450558</v>
+        <v>1106.237683491107</v>
       </c>
     </row>
     <row r="4">
@@ -7812,10 +7812,10 @@
         <v>1277.1445006986</v>
       </c>
       <c r="D4" t="n">
-        <v>1201.301639449933</v>
+        <v>1194.509357929752</v>
       </c>
       <c r="E4" t="n">
-        <v>1352.164800424748</v>
+        <v>1359.65429842013</v>
       </c>
     </row>
     <row r="5">
@@ -7829,10 +7829,10 @@
         <v>1226.275973389348</v>
       </c>
       <c r="D5" t="n">
-        <v>1153.789055580226</v>
+        <v>1150.6309508475</v>
       </c>
       <c r="E5" t="n">
-        <v>1304.317258789016</v>
+        <v>1301.494670390761</v>
       </c>
     </row>
     <row r="6">
@@ -7846,10 +7846,10 @@
         <v>1066.209747390613</v>
       </c>
       <c r="D6" t="n">
-        <v>990.4321881204474</v>
+        <v>985.1887894019046</v>
       </c>
       <c r="E6" t="n">
-        <v>1144.144569958676</v>
+        <v>1140.395168080533</v>
       </c>
     </row>
     <row r="7">
@@ -7863,10 +7863,10 @@
         <v>1172.190424121186</v>
       </c>
       <c r="D7" t="n">
-        <v>1095.062370200265</v>
+        <v>1097.591523004442</v>
       </c>
       <c r="E7" t="n">
-        <v>1243.2216856224</v>
+        <v>1244.047118352827</v>
       </c>
     </row>
     <row r="8">
@@ -7880,10 +7880,10 @@
         <v>943.8127818173346</v>
       </c>
       <c r="D8" t="n">
-        <v>867.1152194069793</v>
+        <v>872.5209265749602</v>
       </c>
       <c r="E8" t="n">
-        <v>1022.324643353636</v>
+        <v>1023.486267600881</v>
       </c>
     </row>
     <row r="9">
@@ -7897,10 +7897,10 @@
         <v>1133.737455466864</v>
       </c>
       <c r="D9" t="n">
-        <v>1057.186350835111</v>
+        <v>1058.749722145839</v>
       </c>
       <c r="E9" t="n">
-        <v>1208.37155029483</v>
+        <v>1210.131025158126</v>
       </c>
     </row>
     <row r="10">
@@ -7914,10 +7914,10 @@
         <v>1024.666652857757</v>
       </c>
       <c r="D10" t="n">
-        <v>951.9316082681914</v>
+        <v>948.3836359400607</v>
       </c>
       <c r="E10" t="n">
-        <v>1094.944590434161</v>
+        <v>1097.990434964254</v>
       </c>
     </row>
     <row r="11">
@@ -7931,10 +7931,10 @@
         <v>1091.678459336561</v>
       </c>
       <c r="D11" t="n">
-        <v>1017.296406431585</v>
+        <v>1015.665168516084</v>
       </c>
       <c r="E11" t="n">
-        <v>1168.428255584106</v>
+        <v>1166.481664534916</v>
       </c>
     </row>
     <row r="12">
@@ -7948,10 +7948,10 @@
         <v>1221.088723357709</v>
       </c>
       <c r="D12" t="n">
-        <v>1148.287289244327</v>
+        <v>1144.792253253248</v>
       </c>
       <c r="E12" t="n">
-        <v>1298.383330078962</v>
+        <v>1297.433874583638</v>
       </c>
     </row>
     <row r="13">
@@ -7965,10 +7965,10 @@
         <v>1241.301288689388</v>
       </c>
       <c r="D13" t="n">
-        <v>1167.065040654189</v>
+        <v>1171.311179432302</v>
       </c>
       <c r="E13" t="n">
-        <v>1319.470306785988</v>
+        <v>1313.405951084167</v>
       </c>
     </row>
     <row r="14">
@@ -7982,10 +7982,10 @@
         <v>987.1628510986411</v>
       </c>
       <c r="D14" t="n">
-        <v>912.9640650226366</v>
+        <v>912.2483615016146</v>
       </c>
       <c r="E14" t="n">
-        <v>1059.856030430295</v>
+        <v>1060.934325332273</v>
       </c>
     </row>
     <row r="15">
@@ -7999,10 +7999,10 @@
         <v>939.0640001252774</v>
       </c>
       <c r="D15" t="n">
-        <v>862.2106049179231</v>
+        <v>864.0745519386128</v>
       </c>
       <c r="E15" t="n">
-        <v>1015.871156728365</v>
+        <v>1018.908083115101</v>
       </c>
     </row>
     <row r="16">
@@ -8016,10 +8016,10 @@
         <v>1129.176588777347</v>
       </c>
       <c r="D16" t="n">
-        <v>1050.616620397224</v>
+        <v>1049.16394117664</v>
       </c>
       <c r="E16" t="n">
-        <v>1205.959539138293</v>
+        <v>1205.17444680472</v>
       </c>
     </row>
     <row r="17">
@@ -8033,10 +8033,10 @@
         <v>1020.293701171131</v>
       </c>
       <c r="D17" t="n">
-        <v>941.8173301199005</v>
+        <v>948.5683513235539</v>
       </c>
       <c r="E17" t="n">
-        <v>1098.885303761622</v>
+        <v>1100.585383692746</v>
       </c>
     </row>
     <row r="18">
@@ -8050,10 +8050,10 @@
         <v>1087.493422652583</v>
       </c>
       <c r="D18" t="n">
-        <v>1011.962653495084</v>
+        <v>1011.463662628417</v>
       </c>
       <c r="E18" t="n">
-        <v>1168.850948420339</v>
+        <v>1165.36901411198</v>
       </c>
     </row>
     <row r="19">
@@ -8067,10 +8067,10 @@
         <v>1101.518025735041</v>
       </c>
       <c r="D19" t="n">
-        <v>1024.111859042127</v>
+        <v>1024.69542965505</v>
       </c>
       <c r="E19" t="n">
-        <v>1179.520103934405</v>
+        <v>1181.191372523827</v>
       </c>
     </row>
     <row r="20">
@@ -8084,10 +8084,10 @@
         <v>1057.401205682918</v>
       </c>
       <c r="D20" t="n">
-        <v>975.4287760228464</v>
+        <v>977.0949340150822</v>
       </c>
       <c r="E20" t="n">
-        <v>1131.229565344566</v>
+        <v>1132.207127098352</v>
       </c>
     </row>
     <row r="21">
@@ -8101,10 +8101,10 @@
         <v>983.6668360913504</v>
       </c>
       <c r="D21" t="n">
-        <v>906.8234281282417</v>
+        <v>906.3187871436044</v>
       </c>
       <c r="E21" t="n">
-        <v>1060.833934838436</v>
+        <v>1061.924280351411</v>
       </c>
     </row>
     <row r="22">
@@ -8118,10 +8118,10 @@
         <v>1116.034691450872</v>
       </c>
       <c r="D22" t="n">
-        <v>1040.037604492842</v>
+        <v>1038.847613884288</v>
       </c>
       <c r="E22" t="n">
-        <v>1186.809735901043</v>
+        <v>1197.943671513613</v>
       </c>
     </row>
     <row r="23">
@@ -8135,10 +8135,10 @@
         <v>946.1534424501208</v>
       </c>
       <c r="D23" t="n">
-        <v>871.3096055422805</v>
+        <v>865.1461903585862</v>
       </c>
       <c r="E23" t="n">
-        <v>1019.392005526424</v>
+        <v>1018.08994805328</v>
       </c>
     </row>
     <row r="24">
@@ -8152,10 +8152,10 @@
         <v>1017.674622842841</v>
       </c>
       <c r="D24" t="n">
-        <v>941.968970833805</v>
+        <v>938.5699514624505</v>
       </c>
       <c r="E24" t="n">
-        <v>1092.479781729391</v>
+        <v>1092.993111805032</v>
       </c>
     </row>
     <row r="25">
@@ -8169,10 +8169,10 @@
         <v>1265.341050657395</v>
       </c>
       <c r="D25" t="n">
-        <v>1191.917690662439</v>
+        <v>1187.894633621342</v>
       </c>
       <c r="E25" t="n">
-        <v>1341.469641455919</v>
+        <v>1344.84705608026</v>
       </c>
     </row>
     <row r="26">
@@ -8186,10 +8186,10 @@
         <v>1215.161545024557</v>
       </c>
       <c r="D26" t="n">
-        <v>1136.302637074607</v>
+        <v>1137.231435145336</v>
       </c>
       <c r="E26" t="n">
-        <v>1295.556416510879</v>
+        <v>1295.521524367384</v>
       </c>
     </row>
     <row r="27">
@@ -8203,10 +8203,10 @@
         <v>1055.721702367908</v>
       </c>
       <c r="D27" t="n">
-        <v>977.0788316451403</v>
+        <v>976.9184391201464</v>
       </c>
       <c r="E27" t="n">
-        <v>1131.057575439195</v>
+        <v>1139.509451875634</v>
       </c>
     </row>
     <row r="28">
@@ -8220,10 +8220,10 @@
         <v>982.3631627816907</v>
       </c>
       <c r="D28" t="n">
-        <v>902.120857677448</v>
+        <v>904.1462221517778</v>
       </c>
       <c r="E28" t="n">
-        <v>1053.488140531503</v>
+        <v>1057.759408877691</v>
       </c>
     </row>
     <row r="29">
@@ -8237,10 +8237,10 @@
         <v>934.8906951503774</v>
       </c>
       <c r="D29" t="n">
-        <v>856.8497835266687</v>
+        <v>857.8747516755571</v>
       </c>
       <c r="E29" t="n">
-        <v>1017.951716461981</v>
+        <v>1016.370253759751</v>
       </c>
     </row>
     <row r="30">
@@ -8254,10 +8254,10 @@
         <v>945.4761524828098</v>
       </c>
       <c r="D30" t="n">
-        <v>866.3518481419716</v>
+        <v>864.2426319806696</v>
       </c>
       <c r="E30" t="n">
-        <v>1027.2583172686</v>
+        <v>1024.246708396379</v>
       </c>
     </row>
     <row r="31">
@@ -8271,10 +8271,10 @@
         <v>1017.310524546682</v>
       </c>
       <c r="D31" t="n">
-        <v>937.2173526332663</v>
+        <v>932.9244210331655</v>
       </c>
       <c r="E31" t="n">
-        <v>1096.167644050062</v>
+        <v>1095.29814293523</v>
       </c>
     </row>
     <row r="32">
@@ -8288,10 +8288,10 @@
         <v>1085.199267704381</v>
       </c>
       <c r="D32" t="n">
-        <v>1009.212972159848</v>
+        <v>1005.776762115263</v>
       </c>
       <c r="E32" t="n">
-        <v>1166.04052105281</v>
+        <v>1164.670564117123</v>
       </c>
     </row>
     <row r="33">
@@ -8305,10 +8305,10 @@
         <v>1099.850254129251</v>
       </c>
       <c r="D33" t="n">
-        <v>1020.315199989477</v>
+        <v>1021.217864951286</v>
       </c>
       <c r="E33" t="n">
-        <v>1180.425849819459</v>
+        <v>1178.156268623829</v>
       </c>
     </row>
     <row r="34">
@@ -8322,10 +8322,10 @@
         <v>1056.485094087706</v>
       </c>
       <c r="D34" t="n">
-        <v>974.5242329615363</v>
+        <v>979.8162337252771</v>
       </c>
       <c r="E34" t="n">
-        <v>1135.302483245</v>
+        <v>1138.732776370794</v>
       </c>
     </row>
     <row r="35">
@@ -8339,10 +8339,10 @@
         <v>983.4397461726254</v>
       </c>
       <c r="D35" t="n">
-        <v>904.4790826306095</v>
+        <v>902.763255441462</v>
       </c>
       <c r="E35" t="n">
-        <v>1067.211496072017</v>
+        <v>1062.76912245218</v>
       </c>
     </row>
     <row r="36">
@@ -8356,10 +8356,10 @@
         <v>936.3431085466991</v>
       </c>
       <c r="D36" t="n">
-        <v>859.5288171434837</v>
+        <v>857.2670093498033</v>
       </c>
       <c r="E36" t="n">
-        <v>1014.668254389672</v>
+        <v>1023.097099735311</v>
       </c>
     </row>
     <row r="37">
@@ -8373,10 +8373,10 @@
         <v>947.2417575501211</v>
       </c>
       <c r="D37" t="n">
-        <v>867.8523422702694</v>
+        <v>865.4380828003438</v>
       </c>
       <c r="E37" t="n">
-        <v>1029.760178727778</v>
+        <v>1031.243904733457</v>
       </c>
     </row>
     <row r="38">
@@ -8390,10 +8390,10 @@
         <v>1019.514597953792</v>
       </c>
       <c r="D38" t="n">
-        <v>936.3802245732433</v>
+        <v>931.7285993409163</v>
       </c>
       <c r="E38" t="n">
-        <v>1103.425536386455</v>
+        <v>1103.229530760419</v>
       </c>
     </row>
     <row r="39">
@@ -8407,10 +8407,10 @@
         <v>1087.716532782599</v>
       </c>
       <c r="D39" t="n">
-        <v>1006.24489249848</v>
+        <v>1005.632705033892</v>
       </c>
       <c r="E39" t="n">
-        <v>1172.330972781565</v>
+        <v>1171.597497152604</v>
       </c>
     </row>
     <row r="40">
@@ -8424,10 +8424,10 @@
         <v>1282.896863874782</v>
       </c>
       <c r="D40" t="n">
-        <v>1205.435485000605</v>
+        <v>1193.539955784949</v>
       </c>
       <c r="E40" t="n">
-        <v>1363.310012456262</v>
+        <v>1364.693043387472</v>
       </c>
     </row>
     <row r="41">
@@ -8441,10 +8441,10 @@
         <v>1059.691380842328</v>
       </c>
       <c r="D41" t="n">
-        <v>970.4160428506098</v>
+        <v>975.0044552094191</v>
       </c>
       <c r="E41" t="n">
-        <v>1148.447931645074</v>
+        <v>1141.420852835292</v>
       </c>
     </row>
     <row r="42">
@@ -8458,10 +8458,10 @@
         <v>986.9592245983722</v>
       </c>
       <c r="D42" t="n">
-        <v>907.8300317235517</v>
+        <v>898.050331935566</v>
       </c>
       <c r="E42" t="n">
-        <v>1069.431291073737</v>
+        <v>1076.778007947586</v>
       </c>
     </row>
     <row r="43">
@@ -8475,10 +8475,10 @@
         <v>940.1757786437037</v>
       </c>
       <c r="D43" t="n">
-        <v>856.2581593598228</v>
+        <v>847.8008056397279</v>
       </c>
       <c r="E43" t="n">
-        <v>1027.358648630213</v>
+        <v>1022.686533134072</v>
       </c>
     </row>
     <row r="44">
@@ -8492,10 +8492,10 @@
         <v>1131.603772314442</v>
       </c>
       <c r="D44" t="n">
-        <v>1044.720254604975</v>
+        <v>1043.018015744801</v>
       </c>
       <c r="E44" t="n">
-        <v>1219.29130587475</v>
+        <v>1217.454922654607</v>
       </c>
     </row>
     <row r="45">
@@ -8509,10 +8509,10 @@
         <v>1024.036289727273</v>
       </c>
       <c r="D45" t="n">
-        <v>939.1459442731255</v>
+        <v>940.2868085654643</v>
       </c>
       <c r="E45" t="n">
-        <v>1109.434051703249</v>
+        <v>1109.715507117815</v>
       </c>
     </row>
     <row r="46">
@@ -8526,10 +8526,10 @@
         <v>1092.551416227172</v>
       </c>
       <c r="D46" t="n">
-        <v>1009.116848554515</v>
+        <v>1009.01157965918</v>
       </c>
       <c r="E46" t="n">
-        <v>1179.915175401055</v>
+        <v>1179.278673470488</v>
       </c>
     </row>
     <row r="47">
@@ -8543,10 +8543,10 @@
         <v>1288.044938990443</v>
       </c>
       <c r="D47" t="n">
-        <v>1201.523635872536</v>
+        <v>1195.68731266733</v>
       </c>
       <c r="E47" t="n">
-        <v>1378.450627290327</v>
+        <v>1376.658336578108</v>
       </c>
     </row>
     <row r="48">
@@ -8560,10 +8560,10 @@
         <v>1065.090009295126</v>
       </c>
       <c r="D48" t="n">
-        <v>988.4868351191399</v>
+        <v>974.0618798396279</v>
       </c>
       <c r="E48" t="n">
-        <v>1150.154720938151</v>
+        <v>1147.92571987007</v>
       </c>
     </row>
     <row r="49">
@@ -8577,10 +8577,10 @@
         <v>1172.824559384031</v>
       </c>
       <c r="D49" t="n">
-        <v>1083.227117017051</v>
+        <v>1084.420301515847</v>
       </c>
       <c r="E49" t="n">
-        <v>1258.209911953512</v>
+        <v>1263.522906219532</v>
       </c>
     </row>
     <row r="50">
@@ -8594,10 +8594,10 @@
         <v>946.2007904385276</v>
       </c>
       <c r="D50" t="n">
-        <v>858.7580708643457</v>
+        <v>852.5025604442374</v>
       </c>
       <c r="E50" t="n">
-        <v>1032.519780043892</v>
+        <v>1035.057316843397</v>
       </c>
     </row>
     <row r="51">
@@ -8611,10 +8611,10 @@
         <v>957.7258227842194</v>
       </c>
       <c r="D51" t="n">
-        <v>876.0089451192757</v>
+        <v>860.870251334753</v>
       </c>
       <c r="E51" t="n">
-        <v>1043.298125153997</v>
+        <v>1049.12947004753</v>
       </c>
     </row>
     <row r="52">
@@ -8628,10 +8628,10 @@
         <v>1030.499769861754</v>
       </c>
       <c r="D52" t="n">
-        <v>937.0491632636781</v>
+        <v>935.0233584311422</v>
       </c>
       <c r="E52" t="n">
-        <v>1116.578510890896</v>
+        <v>1121.414358818041</v>
       </c>
     </row>
     <row r="53">
@@ -8645,10 +8645,10 @@
         <v>1099.265449698536</v>
       </c>
       <c r="D53" t="n">
-        <v>1010.364361347027</v>
+        <v>1002.92292077319</v>
       </c>
       <c r="E53" t="n">
-        <v>1190.819097401552</v>
+        <v>1187.279374539052</v>
       </c>
     </row>
     <row r="54">
@@ -8662,10 +8662,10 @@
         <v>1114.793372802433</v>
       </c>
       <c r="D54" t="n">
-        <v>1024.522320711191</v>
+        <v>1010.917522236354</v>
       </c>
       <c r="E54" t="n">
-        <v>1193.481215741682</v>
+        <v>1202.75681130725</v>
       </c>
     </row>
     <row r="55">
@@ -8679,10 +8679,10 @@
         <v>1072.179872771764</v>
       </c>
       <c r="D55" t="n">
-        <v>980.691073748399</v>
+        <v>967.2246606213122</v>
       </c>
       <c r="E55" t="n">
-        <v>1161.684959267317</v>
+        <v>1165.24058664503</v>
       </c>
     </row>
     <row r="56">
@@ -8696,10 +8696,10 @@
         <v>1180.102337863345</v>
       </c>
       <c r="D56" t="n">
-        <v>1089.109645943821</v>
+        <v>1081.645883661662</v>
       </c>
       <c r="E56" t="n">
-        <v>1274.822472247199</v>
+        <v>1278.994101547536</v>
       </c>
     </row>
     <row r="57">
@@ -8713,10 +8713,10 @@
         <v>953.6038455863246</v>
       </c>
       <c r="D57" t="n">
-        <v>865.1280775999492</v>
+        <v>854.8998316484527</v>
       </c>
       <c r="E57" t="n">
-        <v>1042.453727835705</v>
+        <v>1053.11747760401</v>
       </c>
     </row>
     <row r="58">
@@ -8730,10 +8730,10 @@
         <v>965.3167929347474</v>
       </c>
       <c r="D58" t="n">
-        <v>866.1957342126141</v>
+        <v>861.0894005604224</v>
       </c>
       <c r="E58" t="n">
-        <v>1057.648716412131</v>
+        <v>1064.023233304349</v>
       </c>
     </row>
     <row r="59">
@@ -8747,10 +8747,10 @@
         <v>1038.216016680427</v>
       </c>
       <c r="D59" t="n">
-        <v>947.1455736759893</v>
+        <v>936.1350023559962</v>
       </c>
       <c r="E59" t="n">
-        <v>1133.562165364355</v>
+        <v>1138.493385922842</v>
       </c>
     </row>
     <row r="60">
@@ -8764,10 +8764,10 @@
         <v>1107.106973185788</v>
       </c>
       <c r="D60" t="n">
-        <v>1010.249852190652</v>
+        <v>1002.018615960135</v>
       </c>
       <c r="E60" t="n">
-        <v>1203.241887204925</v>
+        <v>1202.980130400908</v>
       </c>
     </row>
     <row r="61">
@@ -8781,10 +8781,10 @@
         <v>1238.333748899608</v>
       </c>
       <c r="D61" t="n">
-        <v>1137.576746596586</v>
+        <v>1135.403336633962</v>
       </c>
       <c r="E61" t="n">
-        <v>1342.907300592734</v>
+        <v>1337.324135527657</v>
       </c>
     </row>
     <row r="62">
@@ -8798,10 +8798,10 @@
         <v>1080.209311261784</v>
       </c>
       <c r="D62" t="n">
-        <v>981.6679813353765</v>
+        <v>975.4848105728166</v>
       </c>
       <c r="E62" t="n">
-        <v>1174.728931719374</v>
+        <v>1182.347515478727</v>
       </c>
     </row>
     <row r="63">
@@ -8815,10 +8815,10 @@
         <v>1008.040900025593</v>
       </c>
       <c r="D63" t="n">
-        <v>918.6743573495863</v>
+        <v>895.942757332014</v>
       </c>
       <c r="E63" t="n">
-        <v>1108.761488949785</v>
+        <v>1108.208078357329</v>
       </c>
     </row>
     <row r="64">
@@ -8832,10 +8832,10 @@
         <v>961.6959224107006</v>
       </c>
       <c r="D64" t="n">
-        <v>861.628580109891</v>
+        <v>853.2553989454684</v>
       </c>
       <c r="E64" t="n">
-        <v>1060.260380010098</v>
+        <v>1060.813886064552</v>
       </c>
     </row>
     <row r="65">
@@ -8849,10 +8849,10 @@
         <v>973.4088697590839</v>
       </c>
       <c r="D65" t="n">
-        <v>869.8384300051887</v>
+        <v>865.6861445060562</v>
       </c>
       <c r="E65" t="n">
-        <v>1075.57850982032</v>
+        <v>1075.651962855949</v>
       </c>
     </row>
     <row r="66">
@@ -8866,10 +8866,10 @@
         <v>1046.308093504786</v>
       </c>
       <c r="D66" t="n">
-        <v>944.7656152341647</v>
+        <v>929.8619101695541</v>
       </c>
       <c r="E66" t="n">
-        <v>1153.591713413069</v>
+        <v>1153.579834226913</v>
       </c>
     </row>
     <row r="67">
@@ -8883,10 +8883,10 @@
         <v>1115.199050010116</v>
       </c>
       <c r="D67" t="n">
-        <v>1010.508647191809</v>
+        <v>998.5739922914699</v>
       </c>
       <c r="E67" t="n">
-        <v>1219.862116403529</v>
+        <v>1218.621532577081</v>
       </c>
     </row>
     <row r="68">
@@ -8900,10 +8900,10 @@
         <v>1130.789611448333</v>
       </c>
       <c r="D68" t="n">
-        <v>1024.588441051471</v>
+        <v>1010.755837000759</v>
       </c>
       <c r="E68" t="n">
-        <v>1235.917344146475</v>
+        <v>1235.296570658578</v>
       </c>
     </row>
     <row r="69">
@@ -8917,10 +8917,10 @@
         <v>1088.238749751813</v>
       </c>
       <c r="D69" t="n">
-        <v>980.1277022927763</v>
+        <v>968.9906261766403</v>
       </c>
       <c r="E69" t="n">
-        <v>1193.939312378252</v>
+        <v>1195.198133989701</v>
       </c>
     </row>
     <row r="70">
@@ -8934,10 +8934,10 @@
         <v>1015.94506184744</v>
       </c>
       <c r="D70" t="n">
-        <v>920.9463079348075</v>
+        <v>893.1623072079741</v>
       </c>
       <c r="E70" t="n">
-        <v>1122.982492697183</v>
+        <v>1128.324891113902</v>
       </c>
     </row>
     <row r="71">
@@ -8951,10 +8951,10 @@
         <v>969.5374458980803</v>
       </c>
       <c r="D71" t="n">
-        <v>862.584589121293</v>
+        <v>850.6353705900899</v>
       </c>
       <c r="E71" t="n">
-        <v>1080.493871417171</v>
+        <v>1079.250628542921</v>
       </c>
     </row>
     <row r="72">
@@ -8968,10 +8968,10 @@
         <v>981.1251165780603</v>
       </c>
       <c r="D72" t="n">
-        <v>864.8073072833764</v>
+        <v>859.3544875543829</v>
       </c>
       <c r="E72" t="n">
-        <v>1094.345977736878</v>
+        <v>1091.934708629113</v>
       </c>
     </row>
     <row r="73">
@@ -8985,10 +8985,10 @@
         <v>1053.899063655343</v>
       </c>
       <c r="D73" t="n">
-        <v>942.6321642872365</v>
+        <v>938.4358181369831</v>
       </c>
       <c r="E73" t="n">
-        <v>1178.554809609044</v>
+        <v>1163.033604133587</v>
       </c>
     </row>
     <row r="74">
@@ -9002,10 +9002,10 @@
         <v>1122.602105157966</v>
       </c>
       <c r="D74" t="n">
-        <v>1009.006471607772</v>
+        <v>993.1916781056298</v>
       </c>
       <c r="E74" t="n">
-        <v>1236.202646277944</v>
+        <v>1237.979061882607</v>
       </c>
     </row>
     <row r="75">
@@ -9019,10 +9019,10 @@
         <v>1318.220904589754</v>
       </c>
       <c r="D75" t="n">
-        <v>1211.259733580725</v>
+        <v>1188.816540848816</v>
       </c>
       <c r="E75" t="n">
-        <v>1434.038306547019</v>
+        <v>1435.17782772971</v>
       </c>
     </row>
     <row r="76">
@@ -9036,10 +9036,10 @@
         <v>1275.48212789045</v>
       </c>
       <c r="D76" t="n">
-        <v>1164.039992370951</v>
+        <v>1148.829669900896</v>
       </c>
       <c r="E76" t="n">
-        <v>1393.785030463881</v>
+        <v>1395.840283871122</v>
       </c>
     </row>
     <row r="77">
@@ -9053,10 +9053,10 @@
         <v>1022.847010321398</v>
       </c>
       <c r="D77" t="n">
-        <v>904.958927386784</v>
+        <v>889.930118067502</v>
       </c>
       <c r="E77" t="n">
-        <v>1140.2270423149</v>
+        <v>1138.852099916432</v>
       </c>
     </row>
     <row r="78">
@@ -9070,10 +9070,10 @@
         <v>1156.404994031391</v>
       </c>
       <c r="D78" t="n">
-        <v>1034.270815933483</v>
+        <v>1021.603361499213</v>
       </c>
       <c r="E78" t="n">
-        <v>1274.516057321366</v>
+        <v>1274.345651538685</v>
       </c>
     </row>
     <row r="79">
@@ -9087,10 +9087,10 @@
         <v>987.5885967125196</v>
       </c>
       <c r="D79" t="n">
-        <v>865.216604176746</v>
+        <v>851.1725904258495</v>
       </c>
       <c r="E79" t="n">
-        <v>1111.830809756309</v>
+        <v>1108.037531890857</v>
       </c>
     </row>
     <row r="80">
@@ -9104,10 +9104,10 @@
         <v>1060.174628787146</v>
       </c>
       <c r="D80" t="n">
-        <v>946.0723977321016</v>
+        <v>934.2633680823484</v>
       </c>
       <c r="E80" t="n">
-        <v>1184.543377886098</v>
+        <v>1187.64411054569</v>
       </c>
     </row>
     <row r="81">
@@ -9121,10 +9121,10 @@
         <v>1128.627116952844</v>
       </c>
       <c r="D81" t="n">
-        <v>1007.196863521614</v>
+        <v>991.7008735409643</v>
       </c>
       <c r="E81" t="n">
-        <v>1241.941477677758</v>
+        <v>1252.456501332086</v>
       </c>
     </row>
     <row r="82">
@@ -9138,10 +9138,10 @@
         <v>1143.779210051449</v>
       </c>
       <c r="D82" t="n">
-        <v>1027.165636847852</v>
+        <v>1002.043922123179</v>
       </c>
       <c r="E82" t="n">
-        <v>1263.390265195975</v>
+        <v>1281.615119050219</v>
       </c>
     </row>
     <row r="83">
@@ -9155,10 +9155,10 @@
         <v>1100.727241680976</v>
       </c>
       <c r="D83" t="n">
-        <v>977.096723689916</v>
+        <v>957.4219041992234</v>
       </c>
       <c r="E83" t="n">
-        <v>1228.03161618579</v>
+        <v>1231.479013241431</v>
       </c>
     </row>
     <row r="84">
@@ -9172,10 +9172,10 @@
         <v>1027.995085437022</v>
       </c>
       <c r="D84" t="n">
-        <v>898.8310156438841</v>
+        <v>891.6820217877906</v>
       </c>
       <c r="E84" t="n">
-        <v>1169.167087723636</v>
+        <v>1149.976155746756</v>
       </c>
     </row>
     <row r="85">
@@ -9189,10 +9189,10 @@
         <v>981.0863628139197</v>
       </c>
       <c r="D85" t="n">
-        <v>853.7133934741665</v>
+        <v>836.1565401645028</v>
       </c>
       <c r="E85" t="n">
-        <v>1102.281097913533</v>
+        <v>1114.792522864826</v>
       </c>
     </row>
     <row r="86">
@@ -9206,10 +9206,10 @@
         <v>992.1102884857771</v>
       </c>
       <c r="D86" t="n">
-        <v>877.6392233587662</v>
+        <v>858.9625295308962</v>
       </c>
       <c r="E86" t="n">
-        <v>1120.581127377722</v>
+        <v>1130.09301709447</v>
       </c>
     </row>
     <row r="87">
@@ -9223,10 +9223,10 @@
         <v>1064.383128889154</v>
       </c>
       <c r="D87" t="n">
-        <v>932.5904377640227</v>
+        <v>922.0619167427449</v>
       </c>
       <c r="E87" t="n">
-        <v>1189.448836756275</v>
+        <v>1199.231033763571</v>
       </c>
     </row>
     <row r="88">
@@ -9240,10 +9240,10 @@
         <v>1132.4597870498</v>
       </c>
       <c r="D88" t="n">
-        <v>995.93072926692</v>
+        <v>979.2207471827387</v>
       </c>
       <c r="E88" t="n">
-        <v>1265.730893276609</v>
+        <v>1261.230562540673</v>
       </c>
     </row>
     <row r="89">
@@ -9257,10 +9257,10 @@
         <v>1147.298688477241</v>
       </c>
       <c r="D89" t="n">
-        <v>1005.667124914645</v>
+        <v>992.3588087368463</v>
       </c>
       <c r="E89" t="n">
-        <v>1278.853624856408</v>
+        <v>1290.844021477111</v>
       </c>
     </row>
     <row r="90">
@@ -9274,10 +9274,10 @@
         <v>1103.933528435598</v>
       </c>
       <c r="D90" t="n">
-        <v>976.265205299463</v>
+        <v>947.6109279056823</v>
       </c>
       <c r="E90" t="n">
-        <v>1231.265734404363</v>
+        <v>1245.706312178572</v>
       </c>
     </row>
     <row r="91">
@@ -9291,10 +9291,10 @@
         <v>1030.888180520789</v>
       </c>
       <c r="D91" t="n">
-        <v>891.3714261875045</v>
+        <v>872.7119904681118</v>
       </c>
       <c r="E91" t="n">
-        <v>1161.993969990141</v>
+        <v>1166.779058366365</v>
       </c>
     </row>
     <row r="92">
@@ -9308,10 +9308,10 @@
         <v>1163.757142554085</v>
       </c>
       <c r="D92" t="n">
-        <v>1028.701227400147</v>
+        <v>1007.972979860589</v>
       </c>
       <c r="E92" t="n">
-        <v>1308.657923628757</v>
+        <v>1305.522963867764</v>
       </c>
     </row>
     <row r="93">
@@ -9325,10 +9325,10 @@
         <v>1174.467876554865</v>
       </c>
       <c r="D93" t="n">
-        <v>1036.17680101679</v>
+        <v>1014.651902744749</v>
       </c>
       <c r="E93" t="n">
-        <v>1311.527782916018</v>
+        <v>1316.729677545594</v>
       </c>
     </row>
     <row r="94">
@@ -9342,10 +9342,10 @@
         <v>1066.148733956688</v>
       </c>
       <c r="D94" t="n">
-        <v>922.2259362315351</v>
+        <v>907.3371187289248</v>
       </c>
       <c r="E94" t="n">
-        <v>1212.79258470152</v>
+        <v>1211.982469141971</v>
       </c>
     </row>
     <row r="95">
@@ -9359,10 +9359,10 @@
         <v>1133.912200446176</v>
       </c>
       <c r="D95" t="n">
-        <v>985.0992978960677</v>
+        <v>970.1854629392038</v>
       </c>
       <c r="E95" t="n">
-        <v>1278.278078074087</v>
+        <v>1280.956751890922</v>
       </c>
     </row>
     <row r="96">
@@ -9376,10 +9376,10 @@
         <v>1148.375271868208</v>
       </c>
       <c r="D96" t="n">
-        <v>994.7227688264754</v>
+        <v>985.2816600656204</v>
       </c>
       <c r="E96" t="n">
-        <v>1297.088959097988</v>
+        <v>1296.951166922488</v>
       </c>
     </row>
     <row r="97">
@@ -9393,10 +9393,10 @@
         <v>1104.696920155669</v>
       </c>
       <c r="D97" t="n">
-        <v>957.7778968056062</v>
+        <v>931.1475287556329</v>
       </c>
       <c r="E97" t="n">
-        <v>1256.11500863665</v>
+        <v>1256.374966212409</v>
       </c>
     </row>
     <row r="98">
@@ -9410,10 +9410,10 @@
         <v>1031.213103901007</v>
       </c>
       <c r="D98" t="n">
-        <v>877.818747967294</v>
+        <v>852.4456279318279</v>
       </c>
       <c r="E98" t="n">
-        <v>1182.435414652477</v>
+        <v>1189.65554189542</v>
       </c>
     </row>
     <row r="99">
@@ -9427,10 +9427,10 @@
         <v>983.6153596012075</v>
       </c>
       <c r="D99" t="n">
-        <v>825.8571859014824</v>
+        <v>799.9532405643167</v>
       </c>
       <c r="E99" t="n">
-        <v>1153.606355638534</v>
+        <v>1143.061183613888</v>
       </c>
     </row>
     <row r="100">
@@ -9444,10 +9444,10 @@
         <v>993.9502635966801</v>
       </c>
       <c r="D100" t="n">
-        <v>825.9229854346189</v>
+        <v>822.4481444268577</v>
       </c>
       <c r="E100" t="n">
-        <v>1154.695591734845</v>
+        <v>1152.606942941691</v>
       </c>
     </row>
     <row r="101">
@@ -9461,10 +9461,10 @@
         <v>1065.471443989399</v>
       </c>
       <c r="D101" t="n">
-        <v>900.5148517426874</v>
+        <v>891.8319607070255</v>
       </c>
       <c r="E101" t="n">
-        <v>1216.860742957143</v>
+        <v>1224.705435604226</v>
       </c>
     </row>
     <row r="102">
@@ -9478,10 +9478,10 @@
         <v>1313.075233469545</v>
       </c>
       <c r="D102" t="n">
-        <v>1154.342449379643</v>
+        <v>1144.915092237936</v>
       </c>
       <c r="E102" t="n">
-        <v>1473.276998891442</v>
+        <v>1476.494755717292</v>
       </c>
     </row>
     <row r="103">
@@ -9495,10 +9495,10 @@
         <v>1147.071598558584</v>
       </c>
       <c r="D103" t="n">
-        <v>978.7914869007008</v>
+        <v>954.8085507887552</v>
       </c>
       <c r="E103" t="n">
-        <v>1317.632920819721</v>
+        <v>1317.761819949433</v>
       </c>
     </row>
     <row r="104">
@@ -9512,10 +9512,10 @@
         <v>1103.017416840658</v>
       </c>
       <c r="D104" t="n">
-        <v>939.2292220330029</v>
+        <v>918.2560417352523</v>
       </c>
       <c r="E104" t="n">
-        <v>1273.674406693904</v>
+        <v>1270.709434724999</v>
       </c>
     </row>
     <row r="105">
@@ -9529,10 +9529,10 @@
         <v>1029.220408914865</v>
       </c>
       <c r="D105" t="n">
-        <v>863.5373552155114</v>
+        <v>856.5733249812698</v>
       </c>
       <c r="E105" t="n">
-        <v>1198.752020859798</v>
+        <v>1198.876343165166</v>
       </c>
     </row>
     <row r="106">
@@ -9546,10 +9546,10 @@
         <v>981.3094729439662</v>
       </c>
       <c r="D106" t="n">
-        <v>817.5902716167058</v>
+        <v>790.783117929416</v>
       </c>
       <c r="E106" t="n">
-        <v>1148.702258509516</v>
+        <v>1144.596661097151</v>
       </c>
     </row>
     <row r="107">
@@ -9563,10 +9563,10 @@
         <v>1171.484699930361</v>
       </c>
       <c r="D107" t="n">
-        <v>995.9833516913411</v>
+        <v>988.1498151195595</v>
       </c>
       <c r="E107" t="n">
-        <v>1351.961233068207</v>
+        <v>1349.594595304324</v>
       </c>
     </row>
     <row r="108">
@@ -9580,10 +9580,10 @@
         <v>1062.601812324198</v>
       </c>
       <c r="D108" t="n">
-        <v>883.0402226736564</v>
+        <v>868.298767399443</v>
       </c>
       <c r="E108" t="n">
-        <v>1246.032374137028</v>
+        <v>1239.375309323829</v>
       </c>
     </row>
     <row r="109">
@@ -9597,10 +9597,10 @@
         <v>1129.738895471192</v>
       </c>
       <c r="D109" t="n">
-        <v>951.5207728169548</v>
+        <v>932.380060070152</v>
       </c>
       <c r="E109" t="n">
-        <v>1304.248155523336</v>
+        <v>1305.776605682496</v>
       </c>
     </row>
     <row r="110">
@@ -9614,10 +9614,10 @@
         <v>1143.575583551058</v>
       </c>
       <c r="D110" t="n">
-        <v>958.1460955657823</v>
+        <v>952.2838739710265</v>
       </c>
       <c r="E110" t="n">
-        <v>1328.84747617752</v>
+        <v>1327.482537072709</v>
       </c>
     </row>
     <row r="111">
@@ -9631,10 +9631,10 @@
         <v>1099.270848496188</v>
       </c>
       <c r="D111" t="n">
-        <v>913.551024137514</v>
+        <v>905.1510141448396</v>
       </c>
       <c r="E111" t="n">
-        <v>1279.471733248387</v>
+        <v>1272.287972465635</v>
       </c>
     </row>
     <row r="112">
@@ -9648,10 +9648,10 @@
         <v>1025.285925567711</v>
       </c>
       <c r="D112" t="n">
-        <v>828.6458461546716</v>
+        <v>820.9561265259981</v>
       </c>
       <c r="E112" t="n">
-        <v>1208.744882234794</v>
+        <v>1212.91442232393</v>
       </c>
     </row>
     <row r="113">
@@ -9665,10 +9665,10 @@
         <v>977.1244362600356</v>
       </c>
       <c r="D113" t="n">
-        <v>792.8158135090342</v>
+        <v>760.9421279573113</v>
       </c>
       <c r="E113" t="n">
-        <v>1160.71914698155</v>
+        <v>1159.763872819815</v>
       </c>
     </row>
     <row r="114">
@@ -9682,10 +9682,10 @@
         <v>986.9582335815234</v>
       </c>
       <c r="D114" t="n">
-        <v>798.2700159129483</v>
+        <v>765.8799839798506</v>
       </c>
       <c r="E114" t="n">
-        <v>1161.934063524845</v>
+        <v>1173.014415806281</v>
       </c>
     </row>
     <row r="115">
@@ -9699,10 +9699,10 @@
         <v>1058.0409456349</v>
       </c>
       <c r="D115" t="n">
-        <v>865.260463075005</v>
+        <v>843.4070018575215</v>
       </c>
       <c r="E115" t="n">
-        <v>1255.94840879634</v>
+        <v>1244.27805201525</v>
       </c>
     </row>
     <row r="116">
@@ -9716,10 +9716,10 @@
         <v>1124.990113779179</v>
       </c>
       <c r="D116" t="n">
-        <v>920.6709638377318</v>
+        <v>927.5565324131684</v>
       </c>
       <c r="E116" t="n">
-        <v>1326.878764947151</v>
+        <v>1315.418619565636</v>
       </c>
     </row>
     <row r="117">
@@ -9733,10 +9733,10 @@
         <v>1138.70152519055</v>
       </c>
       <c r="D117" t="n">
-        <v>944.8665960060995</v>
+        <v>931.2034847445567</v>
       </c>
       <c r="E117" t="n">
-        <v>1329.203895865753</v>
+        <v>1330.621470438084</v>
       </c>
     </row>
     <row r="118">
@@ -9750,10 +9750,10 @@
         <v>1094.208875133236</v>
       </c>
       <c r="D118" t="n">
-        <v>899.6554288137997</v>
+        <v>872.2310616853731</v>
       </c>
       <c r="E118" t="n">
-        <v>1294.271777436652</v>
+        <v>1276.823016582783</v>
       </c>
     </row>
     <row r="119">
@@ -9767,10 +9767,10 @@
         <v>1020.098675536036</v>
       </c>
       <c r="D119" t="n">
-        <v>812.071483759745</v>
+        <v>800.7839129306487</v>
       </c>
       <c r="E119" t="n">
-        <v>1212.718344415254</v>
+        <v>1209.704614628692</v>
       </c>
     </row>
     <row r="120">
@@ -9784,10 +9784,10 @@
         <v>971.8119095599437</v>
       </c>
       <c r="D120" t="n">
-        <v>770.8058639973154</v>
+        <v>750.1879539401383</v>
       </c>
       <c r="E120" t="n">
-        <v>1184.570507422683</v>
+        <v>1168.227024642689</v>
       </c>
     </row>
     <row r="121">
@@ -9801,10 +9801,10 @@
         <v>981.5830685472545</v>
       </c>
       <c r="D121" t="n">
-        <v>773.6556651724147</v>
+        <v>756.345186569858</v>
       </c>
       <c r="E121" t="n">
-        <v>1174.611052873171</v>
+        <v>1187.205449353257</v>
       </c>
     </row>
     <row r="122">
@@ -9818,10 +9818,10 @@
         <v>1232.694018594205</v>
       </c>
       <c r="D122" t="n">
-        <v>1016.678990370807</v>
+        <v>998.8190204271295</v>
       </c>
       <c r="E122" t="n">
-        <v>1451.35600911184</v>
+        <v>1441.959023892948</v>
       </c>
     </row>
     <row r="123">
@@ -9835,10 +9835,10 @@
         <v>1119.427033742236</v>
       </c>
       <c r="D123" t="n">
-        <v>918.9166319190934</v>
+        <v>890.9745586934073</v>
       </c>
       <c r="E123" t="n">
-        <v>1337.304691743196</v>
+        <v>1324.730103616625</v>
       </c>
     </row>
     <row r="124">
@@ -9852,10 +9852,10 @@
         <v>1133.13844515363</v>
       </c>
       <c r="D124" t="n">
-        <v>918.9363191162738</v>
+        <v>893.1511241870892</v>
       </c>
       <c r="E124" t="n">
-        <v>1350.888920286482</v>
+        <v>1341.477627456409</v>
       </c>
     </row>
     <row r="125">
@@ -9869,10 +9869,10 @@
         <v>1088.64579509621</v>
       </c>
       <c r="D125" t="n">
-        <v>872.0767856371982</v>
+        <v>859.9461925921562</v>
       </c>
       <c r="E125" t="n">
-        <v>1312.655031642081</v>
+        <v>1302.050520321203</v>
       </c>
     </row>
     <row r="126">
@@ -9886,10 +9886,10 @@
         <v>1014.535595499009</v>
       </c>
       <c r="D126" t="n">
-        <v>792.622570354644</v>
+        <v>774.802126294258</v>
       </c>
       <c r="E126" t="n">
-        <v>1238.633049661745</v>
+        <v>1222.654030222125</v>
       </c>
     </row>
     <row r="127">
@@ -9903,10 +9903,10 @@
         <v>966.2488295229477</v>
       </c>
       <c r="D127" t="n">
-        <v>744.3853553937682</v>
+        <v>723.7613293303158</v>
       </c>
       <c r="E127" t="n">
-        <v>1185.739539110505</v>
+        <v>1184.949334905079</v>
       </c>
     </row>
     <row r="128">
@@ -9920,10 +9920,10 @@
         <v>976.0199885103111</v>
       </c>
       <c r="D128" t="n">
-        <v>755.1039250328689</v>
+        <v>728.728778343325</v>
       </c>
       <c r="E128" t="n">
-        <v>1198.262668146177</v>
+        <v>1188.826245963287</v>
       </c>
     </row>
     <row r="129">
@@ -9937,10 +9937,10 @@
         <v>1047.040062229182</v>
       </c>
       <c r="D129" t="n">
-        <v>813.0894646854146</v>
+        <v>802.8025455014514</v>
       </c>
       <c r="E129" t="n">
-        <v>1280.417061358751</v>
+        <v>1272.697618919065</v>
       </c>
     </row>
     <row r="130">
@@ -9954,10 +9954,10 @@
         <v>1114.051868707972</v>
       </c>
       <c r="D130" t="n">
-        <v>872.812195003548</v>
+        <v>865.6437634675917</v>
       </c>
       <c r="E130" t="n">
-        <v>1340.602484979477</v>
+        <v>1347.858144956743</v>
       </c>
     </row>
     <row r="131">
@@ -9971,10 +9971,10 @@
         <v>1127.825918453539</v>
       </c>
       <c r="D131" t="n">
-        <v>893.683113725293</v>
+        <v>894.51012361996</v>
       </c>
       <c r="E131" t="n">
-        <v>1352.367564249294</v>
+        <v>1354.351621794351</v>
       </c>
     </row>
     <row r="132">
@@ -9988,10 +9988,10 @@
         <v>1083.458545064533</v>
       </c>
       <c r="D132" t="n">
-        <v>845.5604407936024</v>
+        <v>837.0123175166844</v>
       </c>
       <c r="E132" t="n">
-        <v>1308.052273175203</v>
+        <v>1313.219679127918</v>
       </c>
     </row>
     <row r="133">
@@ -10005,10 +10005,10 @@
         <v>1009.473622135786</v>
       </c>
       <c r="D133" t="n">
-        <v>769.2389104362094</v>
+        <v>767.8948894591272</v>
       </c>
       <c r="E133" t="n">
-        <v>1237.077832300425</v>
+        <v>1235.808705655442</v>
       </c>
     </row>
     <row r="134">
@@ -10022,10 +10022,10 @@
         <v>961.3747711624385</v>
       </c>
       <c r="D134" t="n">
-        <v>720.9307423563631</v>
+        <v>706.0219720542301</v>
       </c>
       <c r="E134" t="n">
-        <v>1196.688659836311</v>
+        <v>1185.102392699465</v>
       </c>
     </row>
     <row r="135">
@@ -10039,10 +10039,10 @@
         <v>971.2712068183068</v>
       </c>
       <c r="D135" t="n">
-        <v>723.946342294056</v>
+        <v>719.9232161961088</v>
       </c>
       <c r="E135" t="n">
-        <v>1213.782378483823</v>
+        <v>1193.019702526451</v>
       </c>
     </row>
     <row r="136">
@@ -10056,10 +10056,10 @@
         <v>1042.479195539877</v>
       </c>
       <c r="D136" t="n">
-        <v>782.9832973090585</v>
+        <v>775.7849583131708</v>
       </c>
       <c r="E136" t="n">
-        <v>1287.742540732003</v>
+        <v>1269.10192777673</v>
       </c>
     </row>
     <row r="137">
@@ -10073,10 +10073,10 @@
         <v>1109.678917021315</v>
       </c>
       <c r="D137" t="n">
-        <v>854.1891969372623</v>
+        <v>848.5686763242742</v>
       </c>
       <c r="E137" t="n">
-        <v>1354.343319918784</v>
+        <v>1352.924107242566</v>
       </c>
     </row>
     <row r="138">
@@ -10090,10 +10090,10 @@
         <v>1123.640881769518</v>
       </c>
       <c r="D138" t="n">
-        <v>872.1929369143746</v>
+        <v>862.3571645031705</v>
       </c>
       <c r="E138" t="n">
-        <v>1372.220005959276</v>
+        <v>1361.468541129667</v>
       </c>
     </row>
     <row r="139">
@@ -10107,10 +10107,10 @@
         <v>1079.524061717385</v>
       </c>
       <c r="D139" t="n">
-        <v>832.8165748042709</v>
+        <v>806.3968918490802</v>
       </c>
       <c r="E139" t="n">
-        <v>1322.429437071292</v>
+        <v>1323.955120085849</v>
       </c>
     </row>
     <row r="140">
@@ -10124,10 +10124,10 @@
         <v>1005.727053791591</v>
       </c>
       <c r="D140" t="n">
-        <v>748.8856186348881</v>
+        <v>738.9775432576834</v>
       </c>
       <c r="E140" t="n">
-        <v>1248.501457587732</v>
+        <v>1238.306841942264</v>
       </c>
     </row>
     <row r="141">
@@ -10141,10 +10141,10 @@
         <v>957.8787561549021</v>
       </c>
       <c r="D141" t="n">
-        <v>683.0987218200378</v>
+        <v>680.5458816386197</v>
       </c>
       <c r="E141" t="n">
-        <v>1230.18914678844</v>
+        <v>1209.906771240528</v>
       </c>
     </row>
     <row r="142">
@@ -10158,10 +10158,10 @@
         <v>968.0883834819497</v>
       </c>
       <c r="D142" t="n">
-        <v>686.1003612265592</v>
+        <v>683.4141145977758</v>
       </c>
       <c r="E142" t="n">
-        <v>1228.557238516383</v>
+        <v>1223.107127930248</v>
       </c>
     </row>
     <row r="143">
@@ -10175,10 +10175,10 @@
         <v>1039.609563874683</v>
       </c>
       <c r="D143" t="n">
-        <v>785.4291323927904</v>
+        <v>773.9164111881245</v>
       </c>
       <c r="E143" t="n">
-        <v>1296.495996356554</v>
+        <v>1287.934498308126</v>
       </c>
     </row>
     <row r="144">
@@ -10192,10 +10192,10 @@
         <v>1107.059838692997</v>
       </c>
       <c r="D144" t="n">
-        <v>841.0888411247768</v>
+        <v>834.4237938807013</v>
       </c>
       <c r="E144" t="n">
-        <v>1362.476309733422</v>
+        <v>1361.586436758621</v>
       </c>
     </row>
     <row r="145">
@@ -10209,10 +10209,10 @@
         <v>1121.334995112352</v>
       </c>
       <c r="D145" t="n">
-        <v>843.3403170803472</v>
+        <v>844.8218019092445</v>
       </c>
       <c r="E145" t="n">
-        <v>1390.227296059144</v>
+        <v>1368.701908504764</v>
       </c>
     </row>
     <row r="146">
@@ -10226,10 +10226,10 @@
         <v>1077.531366731244</v>
       </c>
       <c r="D146" t="n">
-        <v>783.7246749284826</v>
+        <v>794.6074806192707</v>
       </c>
       <c r="E146" t="n">
-        <v>1351.388717963601</v>
+        <v>1336.448535331116</v>
       </c>
     </row>
     <row r="147">
@@ -10243,10 +10243,10 @@
         <v>1004.047550476575</v>
       </c>
       <c r="D147" t="n">
-        <v>720.7631650415804</v>
+        <v>718.3192420399109</v>
       </c>
       <c r="E147" t="n">
-        <v>1285.158700502944</v>
+        <v>1276.028625516425</v>
       </c>
     </row>
     <row r="148">
@@ -10260,10 +10260,10 @@
         <v>956.5750828453699</v>
       </c>
       <c r="D148" t="n">
-        <v>667.5156531052621</v>
+        <v>664.8991639219649</v>
       </c>
       <c r="E148" t="n">
-        <v>1231.539372308517</v>
+        <v>1229.19626290197</v>
       </c>
     </row>
     <row r="149">
@@ -10277,10 +10277,10 @@
         <v>967.0979018435085</v>
       </c>
       <c r="D149" t="n">
-        <v>689.8413103890509</v>
+        <v>651.0460060256013</v>
       </c>
       <c r="E149" t="n">
-        <v>1230.241604203383</v>
+        <v>1223.675388512037</v>
       </c>
     </row>
     <row r="150">
@@ -10294,10 +10294,10 @@
         <v>1038.932273907394</v>
       </c>
       <c r="D150" t="n">
-        <v>744.2209092848232</v>
+        <v>747.4228534689128</v>
       </c>
       <c r="E150" t="n">
-        <v>1324.632133011571</v>
+        <v>1303.73941822259</v>
       </c>
     </row>
     <row r="151">
@@ -10311,10 +10311,10 @@
         <v>1106.695740396627</v>
       </c>
       <c r="D151" t="n">
-        <v>803.9132996907895</v>
+        <v>803.4758695192547</v>
       </c>
       <c r="E151" t="n">
-        <v>1396.190360188559</v>
+        <v>1389.255417678479</v>
       </c>
     </row>
     <row r="152">
@@ -10328,10 +10328,10 @@
         <v>1121.346726821476</v>
       </c>
       <c r="D152" t="n">
-        <v>824.9566709298407</v>
+        <v>815.0166550358308</v>
       </c>
       <c r="E152" t="n">
-        <v>1414.681126948469</v>
+        <v>1398.861209318283</v>
       </c>
     </row>
     <row r="153">
@@ -10345,10 +10345,10 @@
         <v>1258.009804773461</v>
       </c>
       <c r="D153" t="n">
-        <v>951.9135402720145</v>
+        <v>955.1589060539994</v>
       </c>
       <c r="E153" t="n">
-        <v>1535.020777125133</v>
+        <v>1529.91610172622</v>
       </c>
     </row>
     <row r="154">
@@ -10362,10 +10362,10 @@
         <v>1004.81094219638</v>
       </c>
       <c r="D154" t="n">
-        <v>694.536563888287</v>
+        <v>692.1980117452825</v>
       </c>
       <c r="E154" t="n">
-        <v>1283.229314081135</v>
+        <v>1278.652142421528</v>
       </c>
     </row>
     <row r="155">
@@ -10379,10 +10379,10 @@
         <v>957.6516662363357</v>
       </c>
       <c r="D155" t="n">
-        <v>640.2017375650865</v>
+        <v>641.608905136456</v>
       </c>
       <c r="E155" t="n">
-        <v>1245.671880056153</v>
+        <v>1242.866990921478</v>
       </c>
     </row>
     <row r="156">
@@ -10396,10 +10396,10 @@
         <v>968.5503152396896</v>
       </c>
       <c r="D156" t="n">
-        <v>654.344083496464</v>
+        <v>657.3162689088254</v>
       </c>
       <c r="E156" t="n">
-        <v>1258.87888626476</v>
+        <v>1247.302775353263</v>
       </c>
     </row>
     <row r="157">
@@ -10413,10 +10413,10 @@
         <v>1040.697878974921</v>
       </c>
       <c r="D157" t="n">
-        <v>726.7776131280359</v>
+        <v>733.8798814138039</v>
       </c>
       <c r="E157" t="n">
-        <v>1328.289325417799</v>
+        <v>1343.613194779809</v>
       </c>
     </row>
     <row r="158">
@@ -10430,10 +10430,10 @@
         <v>1108.899813803715</v>
       </c>
       <c r="D158" t="n">
-        <v>794.3964667072884</v>
+        <v>789.2757277030876</v>
       </c>
       <c r="E158" t="n">
-        <v>1404.344144390579</v>
+        <v>1401.074847113614</v>
       </c>
     </row>
     <row r="159">
@@ -10447,10 +10447,10 @@
         <v>1239.500206175211</v>
       </c>
       <c r="D159" t="n">
-        <v>922.5877956371578</v>
+        <v>921.9171694096254</v>
       </c>
       <c r="E159" t="n">
-        <v>1549.065295295016</v>
+        <v>1537.639229763222</v>
       </c>
     </row>
     <row r="160">
@@ -10464,10 +10464,10 @@
         <v>1080.749385194952</v>
       </c>
       <c r="D160" t="n">
-        <v>755.3455297204085</v>
+        <v>776.491292508304</v>
       </c>
       <c r="E160" t="n">
-        <v>1398.173866706387</v>
+        <v>1379.29510185128</v>
       </c>
     </row>
     <row r="161">
@@ -10481,10 +10481,10 @@
         <v>1008.017228950996</v>
       </c>
       <c r="D161" t="n">
-        <v>677.4271787606472</v>
+        <v>690.7456861950297</v>
       </c>
       <c r="E161" t="n">
-        <v>1315.44554358865</v>
+        <v>1307.656726066712</v>
       </c>
     </row>
     <row r="162">
@@ -10498,10 +10498,10 @@
         <v>961.1711446621175</v>
       </c>
       <c r="D162" t="n">
-        <v>640.8549034700889</v>
+        <v>646.7318444514055</v>
       </c>
       <c r="E162" t="n">
-        <v>1265.713379528971</v>
+        <v>1269.267183454004</v>
       </c>
     </row>
     <row r="163">
@@ -10515,10 +10515,10 @@
         <v>972.3829853366547</v>
       </c>
       <c r="D163" t="n">
-        <v>626.451373991439</v>
+        <v>643.7315541670382</v>
       </c>
       <c r="E163" t="n">
-        <v>1295.29629535396</v>
+        <v>1274.426721472697</v>
       </c>
     </row>
     <row r="164">
@@ -10532,10 +10532,10 @@
         <v>1044.906379077272</v>
       </c>
       <c r="D164" t="n">
-        <v>711.18674117533</v>
+        <v>712.9691535683678</v>
       </c>
       <c r="E164" t="n">
-        <v>1359.938990844106</v>
+        <v>1355.261892436427</v>
       </c>
     </row>
     <row r="165">
@@ -10549,10 +10549,10 @@
         <v>1113.421505577167</v>
       </c>
       <c r="D165" t="n">
-        <v>787.431036837625</v>
+        <v>769.6306265831155</v>
       </c>
       <c r="E165" t="n">
-        <v>1429.250498568149</v>
+        <v>1428.389238746578</v>
       </c>
     </row>
     <row r="166">
@@ -10566,10 +10566,10 @@
         <v>1128.698875344181</v>
       </c>
       <c r="D166" t="n">
-        <v>784.5197438537987</v>
+        <v>782.0561477958415</v>
       </c>
       <c r="E166" t="n">
-        <v>1446.194087841981</v>
+        <v>1430.562880091458</v>
       </c>
     </row>
     <row r="167">
@@ -10583,10 +10583,10 @@
         <v>1085.897460310847</v>
       </c>
       <c r="D167" t="n">
-        <v>732.5703330931416</v>
+        <v>740.98518811563</v>
       </c>
       <c r="E167" t="n">
-        <v>1416.292695110689</v>
+        <v>1384.302645314043</v>
       </c>
     </row>
     <row r="168">
@@ -10600,10 +10600,10 @@
         <v>1013.415857403525</v>
       </c>
       <c r="D168" t="n">
-        <v>662.8992556221209</v>
+        <v>674.5553832586285</v>
       </c>
       <c r="E168" t="n">
-        <v>1328.881389551563</v>
+        <v>1333.627400649745</v>
       </c>
     </row>
     <row r="169">
@@ -10617,10 +10617,10 @@
         <v>966.8829647858113</v>
       </c>
       <c r="D169" t="n">
-        <v>602.4180616592398</v>
+        <v>621.7408965610155</v>
       </c>
       <c r="E169" t="n">
-        <v>1293.698082125031</v>
+        <v>1287.303228486324</v>
       </c>
     </row>
     <row r="170">
@@ -10634,10 +10634,10 @@
         <v>978.4079971315273</v>
       </c>
       <c r="D170" t="n">
-        <v>617.775037499852</v>
+        <v>611.7408003451225</v>
       </c>
       <c r="E170" t="n">
-        <v>1316.634849140415</v>
+        <v>1297.450200751231</v>
       </c>
     </row>
     <row r="171">
@@ -10651,10 +10651,10 @@
         <v>1051.181944209075</v>
       </c>
       <c r="D171" t="n">
-        <v>688.6112991577455</v>
+        <v>708.519706480545</v>
       </c>
       <c r="E171" t="n">
-        <v>1370.685519604774</v>
+        <v>1371.482083789849</v>
       </c>
     </row>
     <row r="172">
@@ -10668,10 +10668,10 @@
         <v>1119.884985711436</v>
       </c>
       <c r="D172" t="n">
-        <v>752.8920265795454</v>
+        <v>771.1990388873151</v>
       </c>
       <c r="E172" t="n">
-        <v>1471.561101316766</v>
+        <v>1453.17196954397</v>
       </c>
     </row>
     <row r="173">
@@ -10685,10 +10685,10 @@
         <v>1135.412908815493</v>
       </c>
       <c r="D173" t="n">
-        <v>778.1246942970943</v>
+        <v>768.015843409304</v>
       </c>
       <c r="E173" t="n">
-        <v>1481.290869906413</v>
+        <v>1471.947663051573</v>
       </c>
     </row>
     <row r="174">
@@ -10702,10 +10702,10 @@
         <v>1092.799408784806</v>
       </c>
       <c r="D174" t="n">
-        <v>716.7359795707883</v>
+        <v>718.171081253337</v>
       </c>
       <c r="E174" t="n">
-        <v>1439.743550530889</v>
+        <v>1419.792614517106</v>
       </c>
     </row>
     <row r="175">
@@ -10719,10 +10719,10 @@
         <v>1020.505720880437</v>
       </c>
       <c r="D175" t="n">
-        <v>652.0953669936493</v>
+        <v>640.1272975550975</v>
       </c>
       <c r="E175" t="n">
-        <v>1364.961071799183</v>
+        <v>1356.409013428468</v>
       </c>
     </row>
     <row r="176">
@@ -10736,10 +10736,10 @@
         <v>974.1607432651563</v>
       </c>
       <c r="D176" t="n">
-        <v>589.5477661738221</v>
+        <v>618.1859406225182</v>
       </c>
       <c r="E176" t="n">
-        <v>1304.869399109467</v>
+        <v>1304.329294801729</v>
       </c>
     </row>
     <row r="177">
@@ -10753,10 +10753,10 @@
         <v>985.8110522793773</v>
       </c>
       <c r="D177" t="n">
-        <v>613.7698406311739</v>
+        <v>600.7539059931103</v>
       </c>
       <c r="E177" t="n">
-        <v>1333.891628954731</v>
+        <v>1323.968098209651</v>
       </c>
     </row>
     <row r="178">
@@ -10770,10 +10770,10 @@
         <v>1058.772914359296</v>
       </c>
       <c r="D178" t="n">
-        <v>679.9125416254519</v>
+        <v>684.1610675825606</v>
       </c>
       <c r="E178" t="n">
-        <v>1424.004969578885</v>
+        <v>1403.110977563374</v>
       </c>
     </row>
     <row r="179">
@@ -10787,10 +10787,10 @@
         <v>1127.601232530417</v>
       </c>
       <c r="D179" t="n">
-        <v>733.8206979107747</v>
+        <v>765.8367589617058</v>
       </c>
       <c r="E179" t="n">
-        <v>1486.491789070788</v>
+        <v>1472.101657194552</v>
       </c>
     </row>
     <row r="180">
@@ -10804,10 +10804,10 @@
         <v>1143.254432302883</v>
       </c>
       <c r="D180" t="n">
-        <v>752.4492894785607</v>
+        <v>764.7490575287427</v>
       </c>
       <c r="E180" t="n">
-        <v>1511.147551931054</v>
+        <v>1478.8290199752</v>
       </c>
     </row>
     <row r="181">
@@ -10821,10 +10821,10 @@
         <v>1100.703570606374</v>
       </c>
       <c r="D181" t="n">
-        <v>708.6974069985848</v>
+        <v>718.4797460357153</v>
       </c>
       <c r="E181" t="n">
-        <v>1470.114849125057</v>
+        <v>1460.333764377414</v>
       </c>
     </row>
   </sheetData>
@@ -10871,10 +10871,10 @@
         <v>1365.197339966959</v>
       </c>
       <c r="C2" t="n">
-        <v>1294.397175908564</v>
+        <v>1301.331826610251</v>
       </c>
       <c r="D2" t="n">
-        <v>1436.634879057663</v>
+        <v>1433.644988607084</v>
       </c>
     </row>
     <row r="3">
@@ -10885,10 +10885,10 @@
         <v>1198.109129268954</v>
       </c>
       <c r="C3" t="n">
-        <v>1128.168408415848</v>
+        <v>1126.159010542935</v>
       </c>
       <c r="D3" t="n">
-        <v>1269.526278120502</v>
+        <v>1273.685895170613</v>
       </c>
     </row>
     <row r="4">
@@ -10899,10 +10899,10 @@
         <v>1211.131030128922</v>
       </c>
       <c r="C4" t="n">
-        <v>1140.253016164403</v>
+        <v>1140.340585815934</v>
       </c>
       <c r="D4" t="n">
-        <v>1284.897285635509</v>
+        <v>1278.171149483553</v>
       </c>
     </row>
     <row r="5">
@@ -10913,10 +10913,10 @@
         <v>1278.710881396066</v>
       </c>
       <c r="C5" t="n">
-        <v>1208.755376738863</v>
+        <v>1211.697327269484</v>
       </c>
       <c r="D5" t="n">
-        <v>1348.17668397623</v>
+        <v>1344.476166491217</v>
       </c>
     </row>
     <row r="6">
@@ -10927,10 +10927,10 @@
         <v>1348.356197966861</v>
       </c>
       <c r="C6" t="n">
-        <v>1280.742321317761</v>
+        <v>1277.666476797118</v>
       </c>
       <c r="D6" t="n">
-        <v>1412.722773617744</v>
+        <v>1417.120479310065</v>
       </c>
     </row>
     <row r="7">
@@ -10941,10 +10941,10 @@
         <v>1358.20440991036</v>
       </c>
       <c r="C7" t="n">
-        <v>1291.923449450672</v>
+        <v>1289.824148253905</v>
       </c>
       <c r="D7" t="n">
-        <v>1432.388568765062</v>
+        <v>1427.899740387056</v>
       </c>
     </row>
     <row r="8">
@@ -10955,10 +10955,10 @@
         <v>1316.215605662903</v>
       </c>
       <c r="C8" t="n">
-        <v>1250.093273620375</v>
+        <v>1245.459283063314</v>
       </c>
       <c r="D8" t="n">
-        <v>1383.76101032344</v>
+        <v>1383.429756284222</v>
       </c>
     </row>
     <row r="9">
@@ -10969,10 +10969,10 @@
         <v>1238.438503292802</v>
       </c>
       <c r="C9" t="n">
-        <v>1171.496258447892</v>
+        <v>1166.10521616244</v>
       </c>
       <c r="D9" t="n">
-        <v>1303.685750006316</v>
+        <v>1310.77992578904</v>
       </c>
     </row>
     <row r="10">
@@ -10983,10 +10983,10 @@
         <v>1190.45926748482</v>
       </c>
       <c r="C10" t="n">
-        <v>1124.699396863653</v>
+        <v>1123.785176638984</v>
       </c>
       <c r="D10" t="n">
-        <v>1262.700298010309</v>
+        <v>1263.834091574917</v>
       </c>
     </row>
     <row r="11">
@@ -10997,10 +10997,10 @@
         <v>1202.622690734798</v>
       </c>
       <c r="C11" t="n">
-        <v>1131.267065269186</v>
+        <v>1130.386421936655</v>
       </c>
       <c r="D11" t="n">
-        <v>1273.152167362683</v>
+        <v>1272.485374754322</v>
       </c>
     </row>
     <row r="12">
@@ -11011,10 +11011,10 @@
         <v>1269.235539845295</v>
       </c>
       <c r="C12" t="n">
-        <v>1202.814666748247</v>
+        <v>1204.505427376002</v>
       </c>
       <c r="D12" t="n">
-        <v>1335.741996729473</v>
+        <v>1339.7222399348</v>
       </c>
     </row>
     <row r="13">
@@ -11025,10 +11025,10 @@
         <v>1337.823274307105</v>
       </c>
       <c r="C13" t="n">
-        <v>1271.698738552917</v>
+        <v>1262.31878762994</v>
       </c>
       <c r="D13" t="n">
-        <v>1407.531888385372</v>
+        <v>1409.581997740102</v>
       </c>
     </row>
     <row r="14">
@@ -11039,10 +11039,10 @@
         <v>1346.5436126026</v>
       </c>
       <c r="C14" t="n">
-        <v>1276.261670054751</v>
+        <v>1279.075467796868</v>
       </c>
       <c r="D14" t="n">
-        <v>1413.00790938866</v>
+        <v>1411.733511550047</v>
       </c>
     </row>
     <row r="15">
@@ -11053,10 +11053,10 @@
         <v>1303.378822731287</v>
       </c>
       <c r="C15" t="n">
-        <v>1229.63059217507</v>
+        <v>1233.546702573598</v>
       </c>
       <c r="D15" t="n">
-        <v>1374.2006692719</v>
+        <v>1371.240242449054</v>
       </c>
     </row>
     <row r="16">
@@ -11067,10 +11067,10 @@
         <v>1224.401190791964</v>
       </c>
       <c r="C16" t="n">
-        <v>1158.902158235895</v>
+        <v>1155.108292263189</v>
       </c>
       <c r="D16" t="n">
-        <v>1294.318792183654</v>
+        <v>1294.421230277756</v>
       </c>
     </row>
     <row r="17">
@@ -11081,10 +11081,10 @@
         <v>1295.065016450289</v>
       </c>
       <c r="C17" t="n">
-        <v>1228.334334328604</v>
+        <v>1226.358540614299</v>
       </c>
       <c r="D17" t="n">
-        <v>1361.594818087239</v>
+        <v>1365.292332755973</v>
       </c>
     </row>
     <row r="18">
@@ -11095,10 +11095,10 @@
         <v>1186.20863635084</v>
       </c>
       <c r="C18" t="n">
-        <v>1116.300702276701</v>
+        <v>1115.289014568601</v>
       </c>
       <c r="D18" t="n">
-        <v>1254.564023740948</v>
+        <v>1253.012157530966</v>
       </c>
     </row>
     <row r="19">
@@ -11109,10 +11109,10 @@
         <v>1251.694383508901</v>
       </c>
       <c r="C19" t="n">
-        <v>1181.04940899126</v>
+        <v>1184.092020107618</v>
       </c>
       <c r="D19" t="n">
-        <v>1319.550232811243</v>
+        <v>1319.781601819969</v>
       </c>
     </row>
     <row r="20">
@@ -11123,10 +11123,10 @@
         <v>1319.227549063511</v>
       </c>
       <c r="C20" t="n">
-        <v>1250.275710498348</v>
+        <v>1248.614564625814</v>
       </c>
       <c r="D20" t="n">
-        <v>1384.001048841817</v>
+        <v>1386.960350222387</v>
       </c>
     </row>
     <row r="21">
@@ -11137,10 +11137,10 @@
         <v>1326.987991412354</v>
       </c>
       <c r="C21" t="n">
-        <v>1266.911515073718</v>
+        <v>1257.767303149923</v>
       </c>
       <c r="D21" t="n">
-        <v>1395.417439113651</v>
+        <v>1394.357806077435</v>
       </c>
     </row>
     <row r="22">
@@ -11151,10 +11151,10 @@
         <v>1282.978190115814</v>
       </c>
       <c r="C22" t="n">
-        <v>1211.629086826212</v>
+        <v>1216.668621018733</v>
       </c>
       <c r="D22" t="n">
-        <v>1354.819551458168</v>
+        <v>1355.07632070753</v>
       </c>
     </row>
     <row r="23">
@@ -11165,10 +11165,10 @@
         <v>1203.288242337933</v>
       </c>
       <c r="C23" t="n">
-        <v>1135.899299269636</v>
+        <v>1134.860650026657</v>
       </c>
       <c r="D23" t="n">
-        <v>1271.953049652736</v>
+        <v>1271.713554608324</v>
       </c>
     </row>
     <row r="24">
@@ -11179,10 +11179,10 @@
         <v>1153.543725083804</v>
       </c>
       <c r="C24" t="n">
-        <v>1085.959973340147</v>
+        <v>1084.58190926123</v>
       </c>
       <c r="D24" t="n">
-        <v>1221.143439489707</v>
+        <v>1222.805491257755</v>
       </c>
     </row>
     <row r="25">
@@ -11193,10 +11193,10 @@
         <v>1164.12596553407</v>
       </c>
       <c r="C25" t="n">
-        <v>1093.040677024659</v>
+        <v>1097.243089667583</v>
       </c>
       <c r="D25" t="n">
-        <v>1237.04586500203</v>
+        <v>1230.504911150535</v>
       </c>
     </row>
     <row r="26">
@@ -11207,10 +11207,10 @@
         <v>1229.374543287108</v>
       </c>
       <c r="C26" t="n">
-        <v>1162.161608356429</v>
+        <v>1160.256494297027</v>
       </c>
       <c r="D26" t="n">
-        <v>1296.216352091654</v>
+        <v>1296.502061946636</v>
       </c>
     </row>
     <row r="27">
@@ -11221,10 +11221,10 @@
         <v>1296.843252088046</v>
       </c>
       <c r="C27" t="n">
-        <v>1224.535613361985</v>
+        <v>1228.208044456892</v>
       </c>
       <c r="D27" t="n">
-        <v>1362.879015239019</v>
+        <v>1367.29589247119</v>
       </c>
     </row>
     <row r="28">
@@ -11235,10 +11235,10 @@
         <v>1304.713015826093</v>
       </c>
       <c r="C28" t="n">
-        <v>1233.898593728777</v>
+        <v>1237.983462874572</v>
       </c>
       <c r="D28" t="n">
-        <v>1374.458077217497</v>
+        <v>1368.575550188095</v>
       </c>
     </row>
     <row r="29">
@@ -11249,10 +11249,10 @@
         <v>1260.983651101878</v>
       </c>
       <c r="C29" t="n">
-        <v>1187.670437334061</v>
+        <v>1196.266497410367</v>
       </c>
       <c r="D29" t="n">
-        <v>1332.596730533504</v>
+        <v>1332.596338364891</v>
       </c>
     </row>
     <row r="30">
@@ -11263,10 +11263,10 @@
         <v>1181.738943027161</v>
       </c>
       <c r="C30" t="n">
-        <v>1113.126107122559</v>
+        <v>1116.297949898829</v>
       </c>
       <c r="D30" t="n">
-        <v>1250.373071944668</v>
+        <v>1249.397260426378</v>
       </c>
     </row>
     <row r="31">
@@ -11277,10 +11277,10 @@
         <v>1132.59467373984</v>
       </c>
       <c r="C31" t="n">
-        <v>1061.365904926756</v>
+        <v>1068.293945101737</v>
       </c>
       <c r="D31" t="n">
-        <v>1202.982516316325</v>
+        <v>1203.829192357482</v>
       </c>
     </row>
   </sheetData>
